--- a/app/data/sources/excel/packages_structured_review.xlsx
+++ b/app/data/sources/excel/packages_structured_review.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8676" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8076" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="391">
   <si>
     <t>Packages structured review</t>
   </si>
@@ -159,11 +159,11 @@
     <t>باقه نهار رمضان الشامله</t>
   </si>
   <si>
-    <t>تُعد الفحوصات المخبرية الدورية خطوة أساسية للاطمئنان على صحتك والكشف المبكر عن أي خلل قد يؤثر على جودة حياتك.</t>
-  </si>
-  <si>
     <t>تُعد الفحوصات المخبرية الدورية خطوة أساسية للاطمئنان على صحتك والكشف المبكر عن أي خلل قد يؤثر على جودة حياتك.
-باقة رمضان الشاملة صُممت لتمنحك صورة متكاملة عن حالة الجسم، من السكر والدهون إلى وظائف الكبد والكلى والهرمونات، وذلك بسعر مميز وفي تحليل واحد متكامل يساعدك على المتابعة الصحية بثقة واطمئنان. تفاصيل التحاليل (باقة نهار رمضان تحتوي على 20 تحليل + 3 تحاليل مجانا )
+باقة رمضان الشاملة صُممت لتمنحك صورة متكاملة عن حالة الجسم، من السكر والدهون إلى وظائف الكبد والكلى والهرمونات، وذلك بسعر مميز وفي تحليل واحد متكامل يساعدك على المتابعة الصحية بثقة واطمئنان. تفاصيل التحاليل (باقة نهار رمضان تحتوي على 20 تحليل + 3 تحاليل مجانا )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تشمل الباقة تحاليل شاملة لتقييم:
 صورة الدم الكاملة
 مستوى السكر والأنسولين
@@ -214,9 +214,6 @@
 يعكس التوازن بين إنزيمي AST و ALT، ويعد مؤشرًا مهمًا لتقييم صحة الكبد والكشف عن أي مشاكل مبكرة.</t>
   </si>
   <si>
-    <t>185 ريال</t>
-  </si>
-  <si>
     <t>ريال</t>
   </si>
   <si>
@@ -229,10 +226,10 @@
     <t>باقه ليالي رمضان الشامله</t>
   </si>
   <si>
-    <t>تم تصميم باقة ليالي رمضان لتقديم تحاليل دقيقة وشاملة تساعدك على متابعة وظائف الجسم الأساسية، المعادن، الفيتامينات، ومستوى الحديد خلال شهر رمضان، مع خدمة السحب المنزلي مجانًا + 3…</t>
-  </si>
-  <si>
-    <t>تم تصميم باقة ليالي رمضان لتقديم تحاليل دقيقة وشاملة تساعدك على متابعة وظائف الجسم الأساسية، المعادن، الفيتامينات، ومستوى الحديد خلال شهر رمضان، مع خدمة السحب المنزلي مجانًا + 3 تحاليل مجانا تفاصيل تحاليل باقة ليالي رمضان الشاملة
+    <t>تم تصميم باقة ليالي رمضان لتقديم تحاليل دقيقة وشاملة تساعدك على متابعة وظائف الجسم الأساسية، المعادن، الفيتامينات، ومستوى الحديد خلال شهر رمضان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 الباقة تشمل أهم التحاليل التي تغطي وظائف الكلى، المعادن الأساسية، الفيتامينات، الحديد ومخزون الجسم، وهرمونات الغدة الدرقية.
 وظائف الكلى وفحص النقرس
 Creatinine (كرياتينين): يقيس مدى كفاءة الكلى في تصفية الدم.
@@ -269,10 +266,10 @@
     <t>تحالیل الروكتان</t>
   </si>
   <si>
-    <t>صُممت باقة تحاليل الروكتان لمتابعة صحة الجسم أثناء علاج الروكتان، من خلال مراقبة وظائف الكبد والكلى ونِسَب الدهون في الدم، لضمان سلامة العلاج والكشف المبكر عن أي تغيّرات قد تؤثر…</t>
-  </si>
-  <si>
-    <t>صُممت باقة تحاليل الروكتان لمتابعة صحة الجسم أثناء علاج الروكتان، من خلال مراقبة وظائف الكبد والكلى ونِسَب الدهون في الدم، لضمان سلامة العلاج والكشف المبكر عن أي تغيّرات قد تؤثر على صحتك. التحاليل المدرجة في (تحاليل الروكتان )
+    <t>صُممت باقة تحاليل الروكتان لمتابعة صحة الجسم أثناء علاج الروكتان، من خلال مراقبة وظائف الكبد والكلى ونِسَب الدهون في الدم، لضمان سلامة العلاج والكشف المبكر عن أي تغيّرات قد تؤثر على صحتك.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> التحاليل المدرجة في (تحاليل الروكتان ) و تشمل : 
 1. ALT – إنزيم الكبد 1 (ألانين ترانس أمينيز)
 يقيس نشاط إنزيم الكبد ويُستخدم لمتابعة سلامة خلايا الكبد أثناء العلاج.
 ارتفاعه قد يدل على تأثر الكبد بالأدوية، ويعتبر مؤشرًا مهمًا أثناء الروكتان.
@@ -302,19 +299,16 @@
 ارتفاعه أثناء العلاج يمكن أن يزيد خطر مشاكل القلب والأوعية الدموية، لذا يتم مراقبته بعناية.</t>
   </si>
   <si>
-    <t>79 ريال</t>
-  </si>
-  <si>
     <t>باقة المعادن و الأملاح</t>
   </si>
   <si>
     <t>باقه المعادن و الاملاح</t>
   </si>
   <si>
-    <t>باقة المعادن والأملاح تساعد على تقييم توازن العناصر الأساسية في الجسم، مثل الصوديوم، البوتاسيوم، الكالسيوم، المغنيسيوم، والحديد، والتي تلعب دورًا مهمًا في وظائف العضلات، الأعصاب،…</t>
-  </si>
-  <si>
-    <t>باقة المعادن والأملاح تساعد على تقييم توازن العناصر الأساسية في الجسم، مثل الصوديوم، البوتاسيوم، الكالسيوم، المغنيسيوم، والحديد، والتي تلعب دورًا مهمًا في وظائف العضلات، الأعصاب، القلب، وتوازن السوائل باقة المعادن و الأملاح
+    <t>باقة المعادن والأملاح تساعد على تقييم توازن العناصر الأساسية في الجسم، مثل الصوديوم، البوتاسيوم، الكالسيوم، المغنيسيوم، والحديد، والتي تلعب دورًا مهمًا في وظائف العضلات، الأعصاب، القلب، وتوازن السوائل باقة المعادن و الأملاح</t>
+  </si>
+  <si>
+    <t>تشمل الباقه : 
 1. Zinc – الزنك
 يُعتبر الزنك من أهم المعادن المسؤولة عن تقوية المناعة، التئام الجروح، وتحسين وظائف الدماغ.
 نقصه قد يؤدي إلى تساقط الشعر، ضعف التركيز، تأخر التئام الجروح، وفقدان الشهية.
@@ -363,12 +357,12 @@
     <t>باقه السكري والدهون</t>
   </si>
   <si>
-    <t>باقة السكري والدهون توفر مجموعة شاملة من التحاليل لمتابعة مستوى السكر، مقاومة الإنسولين، والكولسترول تفاصيل تحاليل باقة السكري والدهون تحليل HbA1c يعكس متوسط مستوى السكر في الدم…</t>
-  </si>
-  <si>
     <t>باقة السكري والدهون توفر مجموعة شاملة من التحاليل لمتابعة مستوى السكر، مقاومة الإنسولين، والكولسترول تفاصيل تحاليل باقة السكري والدهون
 تحليل HbA1c
-يعكس متوسط مستوى السكر في الدم خلال آخر 3 أشهر، ويستخدم لتشخيص ومتابعة السكري.
+يعكس متوسط مستوى السكر في الدم خلال آخر 3 أشهر، ويستخدم لتشخيص ومتابعة السكري.</t>
+  </si>
+  <si>
+    <t>تشمل الباقه : 
 تحليل Insulin Level
 يقيس كمية الإنسولين في الدم، ويساعد في تقييم كفاءة البنكرياس.
 تحليل HOMA-IR
@@ -400,7 +394,7 @@
     <t>باقة تحليل وظائف الكبد والكلى تمثل فحصًا شاملاً لتقييم صحة أهم عضوين مسؤولين عن تنقية الجسم وتنظيم عملياته الحيوية.</t>
   </si>
   <si>
-    <t>باقة تحليل وظائف الكبد والكلى تمثل فحصًا شاملاً لتقييم صحة أهم عضوين مسؤولين عن تنقية الجسم وتنظيم عملياته الحيوية.
+    <t xml:space="preserve">
 تشمل الباقة مجموعة من التحاليل الدقيقة التي تقيس وظائف الكبد، الكلى، وإنزيمات الدم لتحديد مدى كفاءة هذه الأعضاء في أ داء مهامها. التحاليل المدرجة في باقة تحليل وظائف الكبد والكلى
 1. ALT – إنزيم الكبد 1 (ألانين ترانس أميناز)
 إنزيم يُفرز من خلايا الكبد، وارتفاع مستواه يشير إلى إجهاد أو التهاب في خلايا الكبد.
@@ -477,7 +471,7 @@
     <t>باقة تحاليل صحة الطفل هي مجموعة من الاختبارات المختصة التي تهدف إلى تقييم صحة الأطفال ومراقبة نموهم وتطورهم العام.</t>
   </si>
   <si>
-    <t>باقة تحاليل صحة الطفل هي مجموعة من الاختبارات المختصة التي تهدف إلى تقييم صحة الأطفال ومراقبة نموهم وتطورهم العام. تشمل هذه الباقة عدة تحاليل هامة توفر معلومات شاملة حول صحة الطفل وتحديد أي مشاكل صحية قد تكون موجودة.
+    <t xml:space="preserve"> تشمل هذه الباقة عدة تحاليل هامة توفر معلومات شاملة حول صحة الطفل وتحديد أي مشاكل صحية قد تكون موجودة.
 إليك تفاصيل التحاليل التي تشملها باقة تحاليل صحة الطفل
 تحليل فيتامين B12
 يساعد على تقييم نمو الجهاز العصبي وتكوين الدم، ويكشف نقص الفيتامين المرتبط بالتعب وضعف التركيز.
@@ -512,11 +506,11 @@
     <t>باقه الصحه الهرمونيه للرجال</t>
   </si>
   <si>
-    <t>باقة الصحة الهرمونية للرجال مخصصة لتقييم صحة البروستاتا ومستوى الهرمونات لدى الرجال.</t>
-  </si>
-  <si>
-    <t>باقة الصحة الهرمونية للرجال مخصصة لتقييم صحة البروستاتا ومستوى الهرمونات لدى الرجال. تساعد هذه التحاليل على متابعة التوازن الهرموني والكشف المبكر عن أي اضطرابات صحية
-تفاصيل تحاليل باقة الصحة الهرمونية للرجال
+    <t>باقة الصحة الهرمونية للرجال مخصصة لتقييم صحة البروستاتا ومستوى الهرمونات لدى الرجال. تساعد هذه التحاليل على متابعة التوازن الهرموني والكشف المبكر عن أي اضطرابات صحية</t>
+  </si>
+  <si>
+    <t>تشمل الباقه : 
+ تفاصيل تحاليل باقة الصحة الهرمونية للرجال
 تحليل LH: يدعم تقييم التوازن الهرموني ومستويات الهرمونات المهمة للجسم.
 تحليل FSH: يقيس كفاءة الغدد المسؤولة عن إنتاج الهرمونات ودورها في الصحة الإنجابية.
 تحليل Prolactin: ارتفاعه قد يؤثر على التوازن الهرموني وقد يقلل مؤقتًا من فرص الإنجاب.
@@ -536,10 +530,10 @@
     <t>باقه الفيتامينات والمعادن</t>
   </si>
   <si>
-    <t>تحليل الفيتامينات والمعادن:</t>
-  </si>
-  <si>
-    <t>تحليل الفيتامينات والمعادن: يوضح عناصر جسمك المهمة ليعزز طاقتك وصحتك اليومية. تفاصيل التحاليل التي تشملها باقة الفيتامينات والمعادن :
+    <t xml:space="preserve">تحليل الفيتامينات والمعادن: يوضح عناصر جسمك المهمة ليعزز طاقتك وصحتك اليومية. </t>
+  </si>
+  <si>
+    <t>تفاصيل التحاليل التي تشملها باقة الفيتامينات والمعادن :
 -فيتامين D :
 يقيس هذا التحليل مستويات فيتامين D في الدم، وهو فيتامين ضروري لصحة العظام، ووظيفة العضلات، وقوة الجهاز المناعي و صحه الجلد
 – فيتامين B12:
@@ -568,10 +562,10 @@
     <t>باقه الصحه الهرمونيه للمراه</t>
   </si>
   <si>
-    <t>باقة الصحة الهرمونية للمرأة تم تصميمها لتقييم التوازن الهرموني للنساء.</t>
-  </si>
-  <si>
-    <t>باقة الصحة الهرمونية للمرأة تم تصميمها لتقييم التوازن الهرموني للنساء. تساعد هذه التحاليل على متابعة انتظام الدورة الشهرية ووظائف الغدد، والكشف المبكر عن أي تغيّرات هرمونية قد تؤثر على الصحة العامة والراحة اليومية تفاصيل التحاليل
+    <t>باقة الصحة الهرمونية للمرأة تم تصميمها لتقييم التوازن الهرموني للنساء. تساعد هذه التحاليل على متابعة انتظام الدورة الشهرية ووظائف الغدد، والكشف المبكر عن أي تغيّرات هرمونية قد تؤثر على الصحة العامة والراحة اليومية</t>
+  </si>
+  <si>
+    <t>تشمل الباقه : 
 هرمون البروجيستيرون: يقيس التغيرات الهرمونية في مراحل مختلفة، ويدعم تقييم التوازن الهرموني العام في الجسم.
 هرمون AMH (Anti-Müllerian Hormone): مؤشر على كفاءة النشاط الهرموني ويساعد في تقييم الحالة الهرمونية بشكل عام.
 هرمون DHEAs (Dehydroepiandrosterone sulfate): مرتبط بوظائف الغدة الكظرية ويساعد في الكشف عن أي خلل هرموني محتمل.
@@ -591,10 +585,10 @@
     <t>باقه تحليل الفيتامينات المتخصصه</t>
   </si>
   <si>
-    <t>تحليل الفيتامينات Multi Vitamins هو اختبار معملي شامل يقيس مستويات عدة فيتامينات أساسية في الدم، مثل ( A , B1, B2 , B6 , C ,E ) ,هذه الفيتامينات تلعب دورًا محوريًا في الحفاظ على…</t>
-  </si>
-  <si>
-    <t>تحليل الفيتامينات Multi Vitamins هو اختبار معملي شامل يقيس مستويات عدة فيتامينات أساسية في الدم، مثل ( A , B1, B2 , B6 , C ,E ) ,هذه الفيتامينات تلعب دورًا محوريًا في الحفاظ على صحة الجسم، بدءًا من تقوية المناعة وصحة العظام، وحتى دعم الجهاز العصبي وصحة الجلد والشعر أهمية تحليل الفيتامينات
+    <t xml:space="preserve">تحليل الفيتامينات Multi Vitamins هو اختبار معملي شامل يقيس مستويات عدة فيتامينات أساسية في الدم، مثل ( A , B1, B2 , B6 , C ,E ) ,هذه الفيتامينات تلعب دورًا محوريًا في الحفاظ على صحة الجسم، بدءًا من تقوية المناعة وصحة العظام، وحتى دعم الجهاز العصبي وصحة الجلد والشعر </t>
+  </si>
+  <si>
+    <t>أهمية تحليل الفيتامينات :
 تشخيص نقص الفيتامينات: يساعد في تحديد ما إذا كان الشخص يعاني من نقص في عنصر معين.
 الوقاية من الأمراض: نقص بعض الفيتامينات قد يؤدي إلى أمراض خطيرة مثل هشاشة العظام أو فقر الدم.
 متابعة الحالة الغذائية: يفيد الأشخاص الذين يتبعون أنظمة غذائية خاصة مثل النباتيين.
@@ -630,10 +624,10 @@
     <t>تحليل الامراض المعديه std urine pcr</t>
   </si>
   <si>
-    <t>باقة STD Urine PCR هي باقة متكاملة للكشف المبكر والدقيق عن أهم العدوى المنقولة جنسيًا باستخدام تقنية PCR الحديثة، التي تتيح اكتشاف الجراثيم والفيروسات بدقة حتى في المراحل المبكرة…</t>
-  </si>
-  <si>
-    <t>باقة STD Urine PCR هي باقة متكاملة للكشف المبكر والدقيق عن أهم العدوى المنقولة جنسيًا باستخدام تقنية PCR الحديثة، التي تتيح اكتشاف الجراثيم والفيروسات بدقة حتى في المراحل المبكرة للعدوى. هذه الباقة مثالية لمن يرغب في متابعة صحته بدقة واطمئنان شامل. أهمية فحص تحليل الأمراض المعدية ( STD Urine PCR )
+    <t>باقة STD Urine PCR هي باقة متكاملة للكشف المبكر والدقيق عن أهم العدوى المنقولة جنسيًا باستخدام تقنية PCR الحديثة، التي تتيح اكتشاف الجراثيم والفيروسات بدقة حتى في المراحل المبكرة للعدوى. هذه الباقة مثالية لمن يرغب في متابعة صحته بدقة واطمئنان شامل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أهمية فحص تحليل الأمراض المعدية ( STD Urine PCR )
 اختبار الميكوبلازما هومينيس (Mycoplasma hominis PCR)
 يكشف عن وجود بكتيريا Mycoplasma hominis التي قد تسبب التهابات في الجهاز التناسلي واضطرابات الخصوبة.
 اختبار اليوريابلازما بارفوم (Ureaplasma parvum PCR)
@@ -661,10 +655,10 @@
     <t>باقه الامراض المعديه pcr</t>
   </si>
   <si>
-    <t>باقة الأمراض المعدية PCR هي باقة شاملة ومتكاملة للكشف المبكر والدقيق عن أهم الأمراض المنقولة جنسيًا.</t>
-  </si>
-  <si>
-    <t>باقة الأمراض المعدية PCR هي باقة شاملة ومتكاملة للكشف المبكر والدقيق عن أهم الأمراض المنقولة جنسيًا. تستخدم الباقة تقنية PCR الحديثة، المعروفة بدقتها العالية، للكشف عن الفيروسات في مراحلها المبكرة حتى قبل ظهور الأعراض. هذه الباقة مثالية للراغبين في متابعة صحتهم بدقة واطمئنان شامل. تفاصيل التحاليل التي تشملها باقة الأمراض المعدية:
+    <t xml:space="preserve">باقة الأمراض المعدية PCR هي باقة شاملة ومتكاملة للكشف المبكر والدقيق عن أهم الأمراض المنقولة جنسيًا. تستخدم الباقة تقنية PCR الحديثة، المعروفة بدقتها العالية، للكشف عن الفيروسات في مراحلها المبكرة حتى قبل ظهور الأعراض. هذه الباقة مثالية للراغبين في متابعة صحتهم بدقة واطمئنان شامل. </t>
+  </si>
+  <si>
+    <t>تفاصيل التحاليل التي تشملها باقة الأمراض المعدية:
 -فيروس الكبد الوبائي C (تقنية الحمض النووي – PCR):
 يكشف عن وجود الفيروس في الدم بدقة عالية حتى قبل ظهور الأعراض أو الأجسام المضادة. يستخدم لتأكيد الإصابة أو متابعة العلاج.
 -فيروس الكبد الوبائي B (تقنية الحمض النووي – PCR):
@@ -686,10 +680,10 @@
     <t>باقه الكشف المبكر عن الاورام للنساء</t>
   </si>
   <si>
-    <t>اقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس.</t>
-  </si>
-  <si>
-    <t>اقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس. تهدف هذه الباقة إلى تشخيص الأورام في مراحلها المبكرة، مما يساعد في زيادة فرص العلاج الناجح وتحسين نتائج العلاج. إليك تفاصيل التحاليل التي تشملها باقة الكشف المبكر عن الأورام للنساء:
+    <t xml:space="preserve">باقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس. تهدف هذه الباقة إلى تشخيص الأورام في مراحلها المبكرة، مما يساعد في زيادة فرص العلاج الناجح وتحسين نتائج العلاج. </t>
+  </si>
+  <si>
+    <t>إليك تفاصيل التحاليل التي تشملها باقة الكشف المبكر عن الأورام للنساء:
 – كاشف أورام القناة الهضمية:
 يتم استخدام هذا الاختبار للكشف عن وجود أورام في الجهاز الهضمي، مثل الأمعاء والمعدة والمريء. يمكن أن يشمل هذا الاختبار فحص البراز للكشف عن وجود دم غير طبيعي أو وجود مواد كيميائية معينة تشير إلى وجود أورام.
 – كاشف أورام الكبد:
@@ -714,10 +708,10 @@
     <t>باقه صحه الغده الدرقیه</t>
   </si>
   <si>
-    <t>باقة تحالیل صحة الغدة الدرقیة ھي مجموعة من الاختبارات والتحالیل التي تھدف إلى تقییم و ظیفة الغدة الدرقیة وتشخیص أي اضطرابات فیھا .</t>
-  </si>
-  <si>
-    <t>باقة تحالیل صحة الغدة الدرقیة ھي مجموعة من الاختبارات والتحالیل التي تھدف إلى تقییم و ظیفة الغدة الدرقیة وتشخیص أي اضطرابات فیھا . تشمل ھذه الباقة عدة تحالیل مھمة لقیاس مستویات الھرمونات المرتبطة بوظیفة الغدة الدرقیة : (TSH) تحلیل الھرمون المحفز للغدة الدرقیة
+    <t xml:space="preserve">باقة تحالیل صحة الغدة الدرقیة ھي مجموعة من الاختبارات والتحالیل التي تھدف إلى تقییم و ظیفة الغدة الدرقیة وتشخیص أي اضطرابات فیھا . </t>
+  </si>
+  <si>
+    <t>تشمل ھذه الباقة عدة تحالیل مھمة لقیاس مستویات الھرمونات المرتبطة بوظیفة الغدة الدرقیة : (TSH) تحلیل الھرمون المحفز للغدة الدرقیة
 یعتبر الھرمون المحفز للغدة الدرقیة مؤشرا رئیسیاً لوظیفة الغدة الدرقیة. یتم إنتاج ھذا الھرمون في الغدة النخامیة في الدماغ و یعمل على تنظیم إفراز ھرمونات الغدة الدرقیة الأخرى
 تحليل مستوى الهرمون المحفز للغدة الدرقية يمكن أن يساعد في تشخيص اضطرابات الغدة الدرقية مثل فرط أو نقص نشاطها
 يعتبر هرمون الغدة الحر ٣
@@ -736,10 +730,10 @@
     <t>باقه التهابات الجهاز الهضمي</t>
   </si>
   <si>
-    <t>باقة تحاليل التهابات الجهاز الهضمي هي مجموعة من الاختبارات المختصة التي تهدف إلى تشخيص وتقييم التهابات الجهاز الهضمي واضطراباته.</t>
-  </si>
-  <si>
-    <t>باقة تحاليل التهابات الجهاز الهضمي هي مجموعة من الاختبارات المختصة التي تهدف إلى تشخيص وتقييم التهابات الجهاز الهضمي واضطراباته. تشمل هذه الباقة عدة تحاليل هامة تساعد في تحديد وجود العوامل المسببة للالتهابات وتقييم درجة الالتهاب وتأثيره على صحة الجهاز الهضمي. إليك تفاصيل التحاليل التي تشملها باقة تحاليل التهابات الجهاز الهضمي:
+    <t xml:space="preserve">باقة تحاليل التهابات الجهاز الهضمي هي مجموعة من الاختبارات المختصة التي تهدف إلى تشخيص وتقييم التهابات الجهاز الهضمي واضطراباته. </t>
+  </si>
+  <si>
+    <t>تشمل هذه الباقة عدة تحاليل هامة تساعد في تحديد وجود العوامل المسببة للالتهابات وتقييم درجة الالتهاب وتأثيره على صحة الجهاز الهضمي. إليك تفاصيل التحاليل التي تشملها باقة تحاليل التهابات الجهاز الهضمي:
 – جرثومة المعدة في البراز:
 يستخدم هذا الاختبار للكشف عن وجود جرثومة المعدة البوابية Helicobacter pylori في البراز. تعتبر جرثومة المعدة البوابية سببًا شائعًا لالتهابات المعدة والأمعاء، ويمكن أن يؤدي وجودها إلى قرحة المعدة والتهاب المعدة المزمن.
 – الدم الخفي في البراز:
@@ -759,10 +753,10 @@
     <t>باقه تحاليل ما قبل العمليات</t>
   </si>
   <si>
-    <t>باقة تحاليل ما قبل العمليات هي مجموعة من الاختبارات والتحاليل التي يتم إجراؤها قبل إجراء عملية جراحية لتقييم حالة المريض وضمان سلامته أثناء العملية وفي مرحلة ما بعد العملية.</t>
-  </si>
-  <si>
-    <t>باقة تحاليل ما قبل العمليات هي مجموعة من الاختبارات والتحاليل التي يتم إجراؤها قبل إجراء عملية جراحية لتقييم حالة المريض وضمان سلامته أثناء العملية وفي مرحلة ما بعد العملية. تشمل هذه الباقة تحاليل مختلفة لتقييم عوامل مختلفة في الجسم والتأكد من عدم وجود أي اضطرابات أو حالات صحية تسبب مشاكل أثناء العملية الجراحية وفي فترة التعافي. إليك تفاصيل التحاليل التي تشملها باقة ماقبل العمليات:
+    <t xml:space="preserve">باقة تحاليل ما قبل العمليات هي مجموعة من الاختبارات والتحاليل التي يتم إجراؤها قبل إجراء عملية جراحية لتقييم حالة المريض وضمان سلامته أثناء العملية وفي مرحلة ما بعد العملية. تشمل هذه الباقة تحاليل مختلفة لتقييم عوامل مختلفة في الجسم والتأكد من عدم وجود أي اضطرابات أو حالات صحية تسبب مشاكل أثناء العملية الجراحية وفي فترة التعافي. </t>
+  </si>
+  <si>
+    <t>إليك تفاصيل التحاليل التي تشملها باقة ماقبل العمليات:
 زمن التخثر:
 يعتبر اختبار زمن التخثر من الاختبارات الهامة في تحاليل ما قبل العمليات. يقيس هذا الاختبار مدى قدرة الدم على التجلط وتكوين الجلطات. يعتبر زمن التخثر مؤشرًا لوظيفة الجهاز التجلطي في الجسم ويساعد في تقييم مخاطر النزيف أو تجلط الدم أثناء العملية الجراحية
 زمن التخثر الجزئي:
@@ -794,7 +788,7 @@
     <t>باقة الوقاية مصممة للكشف المبكر عن الأمراض المعدية والفيروسات الخطيرة لضمان صحتك وسلامتك.</t>
   </si>
   <si>
-    <t>باقة الوقاية مصممة للكشف المبكر عن الأمراض المعدية والفيروسات الخطيرة لضمان صحتك وسلامتك.
+    <t xml:space="preserve">
 تشمل هذه الباقة مجموعة من التحاليل الدقيقة لفحص فيروسات الكبد B وC، فيروس نقص المناعة المكتسبة، الأمراض المنقولة جنسيًا مثل الزهري، الهربس والسيلان.
 الفحص المبكر يساهم في الوقاية، العلاج المبكر، والحفاظ على صحة الفرد والمجتم تفاصيل التحاليل التي تشملها باقة الأمراض المعدية :
 -تحليل فيروس الكبد الوبائي ب:
@@ -817,10 +811,7 @@
     <t>299 ريال</t>
   </si>
   <si>
-    <t>باقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس.</t>
-  </si>
-  <si>
-    <t>باقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس. تهدف هذه الباقة إلى تشخيص الأورام في مراحلها المبكرة، مما يساعد في زيادة فرص العلاج الناجح وتحسين نتائج العلاج. إليك تفاصيل التحاليل التي تشملها باقة الكشف المبكر عن الأورام للنساء:
+    <t xml:space="preserve"> إليك تفاصيل التحاليل التي تشملها باقة الكشف المبكر عن الأورام للنساء:
 – كاشف أورام القناة الهضمية:
 يتم استخدام هذا الاختبار للكشف عن وجود أورام في الجهاز الهضمي، مثل الأمعاء والمعدة والمريء. يمكن أن يشمل هذا الاختبار فحص البراز للكشف عن وجود دم غير طبيعي أو وجود مواد كيميائية معينة تشير إلى وجود أورام.
 – كاشف أورام الكبد:
@@ -833,7 +824,7 @@
 يتم استخدام هذا الاختبار للكشف عن وجود أورام في البنكرياس. يمكن أن يشمل الاختبار فحص مستويات معينة من الإنزيمات البنكرياسية في الدم، والتي يمكن أن تكون مرتفعة في حالة وجود أورام بنكرياسية.</t>
   </si>
   <si>
-    <t>باقة الوقاية مصممة للكشف المبكر عن الأمراض المعدية والفيروسات الخطيرة لضمان صحتك وسلامتك.
+    <t xml:space="preserve">
 تشمل هذه الباقة مجموعة من التحاليل الدقيقة لفحص فيروسات الكبد B وC، فيروس نقص المناعة المكتسبة، الأمراض المنقولة جنسيًا مثل الزهري، الهربس والسيلان.
 الفحص المبكر يساهم في الوقاية، العلاج المبكر، والحفاظ على صحة الفرد والمجتمع تفاصيل التحاليل التي تشملها باقة الأمراض المعدية :
 -تحليل فيروس الكبد الوبائي ب:
@@ -859,10 +850,10 @@
     <t>باقه تحاليل الاجهاض</t>
   </si>
   <si>
-    <t>باقة تحاليل الاجهاض:</t>
-  </si>
-  <si>
-    <t>باقة تحاليل الاجهاض: تساعد في تحديد الأسباب المحتملة للإجهاض المتكرر لتوجيه العلاج المناسب تفاصيل التحاليل التي تشملها باقة تحاليل الاجهاض :
+    <t>باقة تحاليل الاجهاض: تساعد في تحديد الأسباب المحتملة للإجهاض المتكرر لتوجيه العلاج المناسب</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تفاصيل التحاليل التي تشملها باقة تحاليل الاجهاض :
 -كاشف مناعة داء القطط (Toxoplasma IgG):
 تحليل دم يكشف إذا كانت عندك مناعة سابقة ضد داء القطط، وهو مهم للحوامل لأنه قد يؤثر على الجنين.
 – كاشف داء القطط (Toxoplasma IgM):
@@ -887,10 +878,10 @@
     <t>باقه تحاليل الرياضيين</t>
   </si>
   <si>
-    <t>باقة تحاليل الرياضيين:</t>
-  </si>
-  <si>
-    <t>باقة تحاليل الرياضيين: تقيّم صحة الرياضيين وتحدد قدرتهم على التحمل والأداء البد تفاصيل التحاليل التي تشملها باقة تحاليل الرياضيين:
+    <t>باقة تحاليل الرياضيين: تقيّم صحة الرياضيين وتحدد قدرتهم على التحمل والأداء البدني</t>
+  </si>
+  <si>
+    <t>تفاصيل التحاليل التي تشملها باقة تحاليل الرياضيين:
 -هرمون محفز الغدة الدرقية :
 فحص دم يُستخدم لتقييم وظيفة الغدة الدرقية. TSH هو هرمون ينتجه الدماغ في الغدة النخامية ويعمل على تحفيز الغدة الدرقية لإفراز هرمونات الدرقية المهمة مثل T3 وT4.
 -وظائف الكلى (يوريا) :
@@ -928,10 +919,10 @@
     <t>باقه متابعه ابر المونجارو</t>
   </si>
   <si>
-    <t>يساعد متابعة ابر المونجارو هذا الفحص في التأكد من مدى ملاءمة الإبر لحالتك الصحية قبل البدء في استخدامها، كما يتم إجراؤها بانتظام أثناء فترة الاستخدام لمتابعة مستويات الفيتامينات…</t>
-  </si>
-  <si>
-    <t>يساعد متابعة ابر المونجارو هذا الفحص في التأكد من مدى ملاءمة الإبر لحالتك الصحية قبل البدء في استخدامها، كما يتم إجراؤها بانتظام أثناء فترة الاستخدام لمتابعة مستويات الفيتامينات والمعادن في الجسم. هذا يضمن استمرارية فعالية العلاج وعدم تأثيره على توازن الفيتامينات الضرورية لصحتك. تفاصيل التحاليل التي تشملها باقة متابعة ابر المونجارو :
+    <t xml:space="preserve">يساعد متابعة ابر المونجارو هذا الفحص في التأكد من مدى ملاءمة الإبر لحالتك الصحية قبل البدء في استخدامها، كما يتم إجراؤها بانتظام أثناء فترة الاستخدام لمتابعة مستويات الفيتامينات والمعادن في الجسم. هذا يضمن استمرارية فعالية العلاج وعدم تأثيره على توازن الفيتامينات الضرورية لصحتك. </t>
+  </si>
+  <si>
+    <t>تفاصيل التحاليل التي تشملها باقة متابعة ابر المونجارو :
 – هرمون الغدة الدرقية الحر T4 :
 هو أحد الهرمونات الرئيسية التي تفرزها الغدة الدرقية وله دور مهم في العديد من العمليات البيولوجية، بما في ذلك التمثيل الغذائي (الأيض)، معدل ضربات القلب، والنمو والتطور. تحليل T4 الحر مفيد في تقييم وظيفة الغدة الدرقية ويستخدم بشكل رئيسي لتشخيص حالات فرط نشاط الدرقية.
 – هرمون الغدة الدرقية الحر T3 :
@@ -950,17 +941,31 @@
 تحليل دم يقيس إنزيم مسؤول عن هضم الدهون، وارتفاعه غالبًا يكون مؤشر على التهاب البنكرياس</t>
   </si>
   <si>
+    <t>باقة تحاليل التهابات الجهاز الهضمي هي مجموعة من الاختبارات المختصة التي تهدف إلى تشخيص وتقييم التهابات الجهاز الهضمي واضطراباته. تشمل هذه الباقة عدة تحاليل هامة تساعد في تحديد وجود العوامل المسببة للالتهابات وتقييم درجة الالتهاب وتأثيره على صحة الجهاز الهضمي.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إليك تفاصيل التحاليل التي تشملها باقة تحاليل التهابات الجهاز الهضمي:
+– جرثومة المعدة في البراز:
+يستخدم هذا الاختبار للكشف عن وجود جرثومة المعدة البوابية Helicobacter pylori في البراز. تعتبر جرثومة المعدة البوابية سببًا شائعًا لالتهابات المعدة والأمعاء، ويمكن أن يؤدي وجودها إلى قرحة المعدة والتهاب المعدة المزمن.
+– الدم الخفي في البراز:
+يستخدم هذا الاختبار للكشف عن وجود دم غير مرئي في البراز. قد يشير وجود الدم الخفي إلى وجود تقرحات أو الالتهابات في القناة الهضمية، مثل قرحة الأمعاء الدقيقة، أورام القولون، أو التهاب القولون التقرحي.
+– جرثومة المعدة بالتنفس:
+يستخدم هذا الاختبار للكشف عن وجود جرثومة المعدة البوابية بواسطة تحليل عينة من الهواء المستنشق. يعتبر هذا الاختبار بديلاً غير غازي لاختبار جرثومة المعدة في البراز ويستخدم في بعض الحالات لتشخيص الالتهابات المعدية.
+– تحليل البراز:
+يستخدم هذا الاختبار لتقييم تركيب ووظيفة البراز والكشف عن أي تغيرات غير طبيعية فيه. يمكن أن يساعد تحليل البراز في تشخيص الالتهابات البكتيرية أو الفيروسية في الجهاز الهضمي وتقييم وظائف الكبد والبنكرياس.</t>
+  </si>
+  <si>
     <t>باقة صحة الشعر</t>
   </si>
   <si>
     <t>باقه صحه الشعر</t>
   </si>
   <si>
-    <t>باقة تحاليل تساقط الشعر مصممة لتقييم الصحة العامة للشعر من الداخل من خلال فحوصات دقيقة تشمل الدم، الغدة الدرقية، مخزون الحديد، المعادن، والفيتامينات الأساسية.</t>
-  </si>
-  <si>
     <t>باقة تحاليل تساقط الشعر مصممة لتقييم الصحة العامة للشعر من الداخل من خلال فحوصات دقيقة تشمل الدم، الغدة الدرقية، مخزون الحديد، المعادن، والفيتامينات الأساسية.
-تساعد الباقة في الكشف المبكر عن نقص العناصر الغذائية أو الهرمونات المؤثرة على نمو الشعر وقوة بصيلاته. تفاصيل التحاليل التي تشملها باقة جمال صحة الشعر ( تحليل تساقط الشعر ) :
+تساعد الباقة في الكشف المبكر عن نقص العناصر الغذائية أو الهرمونات المؤثرة على نمو الشعر وقوة بصيلاته.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تفاصيل التحاليل التي تشملها باقة جمال صحة الشعر ( تحليل تساقط الشعر ) :
 1. صورة الدم الكاملة (CBC)
 الكشف عن فقر الدم أو نقص كريات الدم الحمراء، واللي بيؤدي لضعف وصول الأكسجين لبصيلات الشعر وبالتالي التساقط.
 2. الحديد (Iron)
@@ -990,10 +995,10 @@
     <t>باقه متابعه عمليه التكميم</t>
   </si>
   <si>
-    <t>باقة متابعه عملية التكميم:</t>
-  </si>
-  <si>
-    <t>باقة متابعه عملية التكميم: تراقب صحة المريض بعد عملية تكميم المعدة لضمان تعافي الجسم بشكل سليم وقياس معدل الفيتامينات التي ممكن ان تتأثر بعمليات التكميم تفاصيل التحاليل التي تشملها باقة متابعة عملية التكميم :
+    <t xml:space="preserve">باقة متابعه عملية التكميم: تراقب صحة المريض بعد عملية تكميم المعدة لضمان تعافي الجسم بشكل سليم وقياس معدل الفيتامينات التي ممكن ان تتأثر بعمليات التكميم </t>
+  </si>
+  <si>
+    <t>تفاصيل التحاليل التي تشملها باقة متابعة عملية التكميم :
 -صورة الدم الكاملة:
 هي اختبار دم يقدم معلومات عن خلايا الدم في الجسم. يتضمن هذا التحليل عدد وأنواع خلايا الدم الحمراء والبيضاء والصفائح الدموية. يُستخدم للكشف عن مشاكل صحية مثل الأنيميا أو العدوى ويعطي فكرة عامة عن حالة صحة الشخص
 -الصوديوم ، البوتاسيوم الكلوريد :
@@ -1016,10 +1021,10 @@
     <t>باقه نمو الشعر الزايد</t>
   </si>
   <si>
-    <t>باقة نمو الشعر الزائد :</t>
-  </si>
-  <si>
-    <t>باقة نمو الشعر الزائد : تساهم في تشخيص أسباب نمو الشعر الزائد وتقديم حلول علاجية فعّالة
+    <t>باقة نمو الشعر الزائد : تساهم في تشخيص أسباب نمو الشعر الزائد وتقديم حلول علاجية فعّالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل التحاليل التي تشملها باقة نمو الشعر الزائد :
 -هرمون الذكورة الكلي (Testosterone Total):
 يقيس مستوى هرمون التستوستيرون في الدم، وهو المسؤول عن الرغبة الجنسية، نمو العضلات، وصحة العظام. مفيد لتقييم حالات ضعف الخصوبة أو اضطراب الهرمونات.
@@ -1042,7 +1047,7 @@
     <t>باقة تحالیل فحص السكري ھي مجموعة من الاختبارات المختصة التي تھدف إلى تشخیص ومتابعة مرض السكري ومراقبة مستویات السكر في الدم.</t>
   </si>
   <si>
-    <t>باقة تحالیل فحص السكري ھي مجموعة من الاختبارات المختصة التي تھدف إلى تشخیص ومتابعة مرض السكري ومراقبة مستویات السكر في الدم. فحص السكري (اختبار الجلوكوز في الدم)
+    <t xml:space="preserve"> فحص السكري (اختبار الجلوكوز في الدم)
 یستخدم ھذا الاختبار لقیاس مستوى السكر في الدم عن طریق أخذ عینة من الدم. ُیعتبر فحص السكري أداة أساسیة لتشخیص السكري ومراقبة مستویات السكر في الدم. یتم تقییم النتائج بنا ًء على القیم الطبیعیة المعتمدة للسكر في الدم في الحالة الصائمة أو بعد تناول وجبة
 السكر التراكمي (اختبار الھیموغلوبین)
 یستخدم ھذا الاختبار لقیاس مستوى السكر في الدم على مدى الشھور السابقة. یعكس السكر التراكمي متوسط مستویات السكر في الدم خلال فترة زمنیة محددة، ویستخدم لتقییم درجة السیطرة على السكر في الدم على المدى ا لطویل . يعرف أيضاً باسم اختبار (HbA1c)
@@ -1058,10 +1063,10 @@
     <t>باقه صحه العظام</t>
   </si>
   <si>
-    <t>باقة صحة العظام مخصصة لتقييم العناصر الأساسية المسؤولة عن قوة العظام وصحتها، حيث تساعد على الكشف المبكر عن نقص المعادن والفيتامينات المهمة للوقاية من هشاشة العظام وضعفها تفاصيل…</t>
-  </si>
-  <si>
-    <t>باقة صحة العظام مخصصة لتقييم العناصر الأساسية المسؤولة عن قوة العظام وصحتها، حيث تساعد على الكشف المبكر عن نقص المعادن والفيتامينات المهمة للوقاية من هشاشة العظام وضعفها تفاصيل التحاليل
+    <t>باقة صحة العظام مخصصة لتقييم العناصر الأساسية المسؤولة عن قوة العظام وصحتها، حيث تساعد على الكشف المبكر عن نقص المعادن والفيتامينات المهمة للوقاية من هشاشة العظام وضعفها</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تفاصيل التحاليل
 فيتامين د (Vitamin D):
 عنصر أساسي لصحة العظام وامتصاص الكالسيوم، ونقصه يرتبط بضعف العظام والعضلات وزيادة خطر الإصابة بالكسور.
 الكالسيوم (Calcium):
@@ -1078,10 +1083,10 @@
     <t>فحص الزواج للغير السعوديين</t>
   </si>
   <si>
-    <t>تشمل باقة فحص الزواج للغير السعوديين تحاليل الكبد الوبائي ب و سي و فايروس نقص المناعة المكتسبة:</t>
-  </si>
-  <si>
-    <t>تشمل باقة فحص الزواج للغير السعوديين تحاليل الكبد الوبائي ب و سي و فايروس نقص المناعة المكتسبة: تكشف لك عن الفيروسات المعدية التي تنتقل جنسيا او عن طريق الدم . الهيموجلوبين الكهربائي: لكشف عن انواع فقر الدم الوراثي كالثلاسيميا و الأنيميا المنجلية .هنالك باقة فحص زواج للسعوديين إلیك تفاصیل التحالیل التي تشملھا باقة فحص الزواج لغير السعوديين:
+    <t xml:space="preserve">تشمل باقة فحص الزواج للغير السعوديين تحاليل الكبد الوبائي ب و سي و فايروس نقص المناعة المكتسبة: تكشف لك عن الفيروسات المعدية التي تنتقل جنسيا او عن طريق الدم . الهيموجلوبين الكهربائي: لكشف عن انواع فقر الدم الوراثي كالثلاسيميا و الأنيميا المنجلية .هنالك باقة فحص زواج للسعوديين </t>
+  </si>
+  <si>
+    <t>إلیك تفاصیل التحالیل التي تشملھا باقة فحص الزواج لغير السعوديين:
 فيروس نقص المناعه المكتسبة :
 يتم جمع عينة من الدم للبحث عن وجود الأجسام المضاده لفيروس HIV
 الهيموجلوبين الكهربائي:
@@ -1105,10 +1110,10 @@
     <t>باقه الكشف المبكر عن الاورام للرجال</t>
   </si>
   <si>
-    <t>باقة تحاليل الكشف المبكر عن الأورام للرجال هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والبروستاتا والبنكرياس والخصية.</t>
-  </si>
-  <si>
-    <t>باقة تحاليل الكشف المبكر عن الأورام للرجال هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والبروستاتا والبنكرياس والخصية. يهدف هذا النوع من التحاليل إلى تشخيص الأورام في مراحلها المبكرة، حيث يمكن أن يكون العلاج أكثر فاعلية وفرص الشفاء أعلى إليك تفاصيل التحاليل التي تشملها باقة الكشف المبكر عن الأورام للرجال:
+    <t>باقة تحاليل الكشف المبكر عن الأورام للرجال هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والبروستاتا والبنكرياس والخصية. يهدف هذا النوع من التحاليل إلى تشخيص الأورام في مراحلها المبكرة، حيث يمكن أن يكون العلاج أكثر فاعلية وفرص الشفاء أعلى</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إليك تفاصيل التحاليل التي تشملها باقة الكشف المبكر عن الأورام للرجال:
 – كاشف أورام القناة الهضمية:
 يتم استخدام هذا الاختبار للكشف عن وجود أورام في الجهاز الهضمي، مثل الأمعاء والمعدة والمريء. يمكن أن يشمل هذا الاختبار فحص البراز للكشف عن وجود دم غير طبيعي أو وجود مواد كيميائية معينة تشير إلى وجود أورام.
 – كاشف أورام الكبد:
@@ -1127,10 +1132,10 @@
     <t>تفاصيل باقه تحاليل فقر الدم</t>
   </si>
   <si>
-    <t>باقة تحاليل فقر الدم :</t>
-  </si>
-  <si>
-    <t>باقة تحاليل فقر الدم : تساعد في تشخيص أنواع فقر الدم وتوجيه العلاج المناسب لتجنب مضاعفاته
+    <t>باقة تحاليل فقر الدم : تساعد في تشخيص أنواع فقر الدم وتوجيه العلاج المناسب لتجنب مضاعفاته</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 إليك تفاصيل التحاليل التي تشملها باقة تحاليل فقر الدم:
 – صورة الدم الكاملة (CBC):
 يقيس عدد وأنواع خلايا الدم المختلفة، بما في ذلك خلايا الدم الحمراء، البيضاء والصفائح الدموية. يُستخدم للكشف عن مشاكل صحية مثل الأنيميا أو العدوى وأمراض الدم الأخرى. ويعطي فكرة عامة عن حالة صحة الشخص
@@ -1154,10 +1159,10 @@
     <t>باقه وظايف الكلي</t>
   </si>
   <si>
-    <t>باقة تحالیل وظائف الكلى ھي مجموعة من الاختبارات المختصة التي تقیم وظیفة الكلى وتساعد في تشخیص ومتابعة الأمراض المرتبطة بھا.</t>
-  </si>
-  <si>
-    <t>باقة تحالیل وظائف الكلى ھي مجموعة من الاختبارات المختصة التي تقیم وظیفة الكلى وتساعد في تشخیص ومتابعة الأمراض المرتبطة بھا. تعتبر الكلى أعضاء حیویة في الجسم تقوم بعدة وظائف مھمة إليك تفاصيل التحاليل التي تشملها باقة وظائف الكلى:
+    <t xml:space="preserve">باقة تحالیل وظائف الكلى ھي مجموعة من الاختبارات المختصة التي تقیم وظیفة الكلى وتساعد في تشخیص ومتابعة الأمراض المرتبطة بھا. تعتبر الكلى أعضاء حیویة في الجسم تقوم بعدة وظائف مھمة </t>
+  </si>
+  <si>
+    <t>إليك تفاصيل التحاليل التي تشملها باقة وظائف الكلى:
 وظائف الكلى (يوريا)
 یتم قیاس مستوى الیوریا في الدم. الیوریا ھي فضلات ناتجة عن عملیة استقلاب البروتین في الجسم. ارتفاع مستوى الیوریا یشیر إلى اضطراب في وظیفة الكلى وقد یكون دلیلاً على خلل في عملیة التصفیة
 وظائف الكلى (كریاتینین)
@@ -1181,10 +1186,10 @@
     <t>تفاصيل باقه تحاليل حساسيه القمح</t>
   </si>
   <si>
-    <t>باقة تحاليل حساسية القمح هي مجموعة من الاختبارات المختصة التي تهدف إلى تحديد استجابة الجسم للقمح ومنتجاته.</t>
-  </si>
-  <si>
-    <t>باقة تحاليل حساسية القمح هي مجموعة من الاختبارات المختصة التي تهدف إلى تحديد استجابة الجسم للقمح ومنتجاته. تتضمن هذه الباقة التحاليل التالية: تحليل حساسية القمح 1، وتحليل حساسية القمح 3
+    <t>باقة تحاليل حساسية القمح هي مجموعة من الاختبارات المختصة التي تهدف إلى تحديد استجابة الجسم للقمح ومنتجاته. تتضمن هذه الباقة التحاليل التالية: تحليل حساسية القمح 1، وتحليل حساسية القمح 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل التحاليل التي تشملها باقة حساسية القمح :
 – تحليل حساسية القمح 1 (IgA):
 يفحص وجود أجسام مضادة تشير إلى تحسس الجسم من بروتين القمح (الجلوتين)، ويستخدم غالبًا لاكتشاف مرض السيلياك أو التحسس من القمح.
@@ -1198,10 +1203,10 @@
     <t>باقه التخسيس وثبات الوزن</t>
   </si>
   <si>
-    <t>تحلل العوامل اللي تأثر على الحرق مثل الغدة والفيتامينات.</t>
-  </si>
-  <si>
-    <t>تحلل العوامل اللي تأثر على الحرق مثل الغدة والفيتامينات. مثالية للي يحاولون ينزلون وزنهم أو يعانون من ثبات ا لوزن
+    <t>تحلل العوامل اللي تأثر على الحرق مثل الغدة والفيتامينات. مثالية للي يحاولون ينزلون وزنهم أو يعانون من ثبات ا لوزن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل التحاليل التي تشملها باقة الفيتامينات والمعادن :
 – صورة الدم الكاملة (CBC):
 يقيس عدد وأنواع خلايا الدم المختلفة، بما في ذلك خلايا الدم الحمراء، البيضاء والصفائح الدموية. ويمكن أن يكشف عن فقر الدم، العدوى، وأمراض الدم الأخرى.
@@ -1253,10 +1258,10 @@
     <t>باقه القولون العصبي</t>
   </si>
   <si>
-    <t>تشمل باقة القولون العصبي ال أورام القناة الهضمية (CEA وCA 19-9)، فيتامين B12، تحليل البراز، ومؤشرات التهاب الأمعاء والقولون.</t>
-  </si>
-  <si>
-    <t>تشمل باقة القولون العصبي ال أورام القناة الهضمية (CEA وCA 19-9)، فيتامين B12، تحليل البراز، ومؤشرات التهاب الأمعاء والقولون. الباقة تشمل زيارة منزلية واستشارة طبية مجانًا، ولا تحتاج إلى صيام. – كاشف الأورام في القناة الهضمية:
+    <t>تشمل باقة القولون العصبي ال أورام القناة الهضمية (CEA وCA 19-9)، فيتامين B12، تحليل البراز، ومؤشرات التهاب الأمعاء والقولون. الباقة تشمل زيارة منزلية واستشارة طبية مجانًا، ولا تحتاج إلى صيام. – كاشف الأورام في القناة الهضمية:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 يشمل اختبارات مثل CEA وCA 19-9، التي تساعد في مراقبة العلاج وكشف الانتكاس في بعض أنواع السرطان بالقناة الهضمية
 – فيتامين B12:
 يقيس مقدار فيتامين B12 في الدم، وهو ضروري لتكوين الحمض النووي، الخلايا العصبية وكريات الدم الحمراء وكذلك للوظائف الإدراكية.
@@ -1272,10 +1277,10 @@
     <t>باقه تحالیل الحساسیه</t>
   </si>
   <si>
-    <t>باقة تحالیل الحساسیة ھي مجموعة من الاختبارات المختصة التي تھدف إلى تشخیص وتحدید التحسس أو الحساسیة لمجموعة معینة من المواد أو العوامل.</t>
-  </si>
-  <si>
-    <t>باقة تحالیل الحساسیة ھي مجموعة من الاختبارات المختصة التي تھدف إلى تشخیص وتحدید التحسس أو الحساسیة لمجموعة معینة من المواد أو العوامل. تعتبر التحالیل المشتركة في ھذه الباقة ھي تحلیل حساسیة الغذاء وتحلیل حساسیة التنفس.
+    <t>باقة تحالیل الحساسیة ھي مجموعة من الاختبارات المختصة التي تھدف إلى تشخیص وتحدید التحسس أو الحساسیة لمجموعة معینة من المواد أو العوامل. تعتبر التحالیل المشتركة في ھذه الباقة ھي تحلیل حساسیة الغذاء وتحلیل حساسیة التنفس.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 إليك تفاصيل التحاليل التي تشملها باقة الحساسية :
 – تحليل حساسية الغذاء:
 يحدد الأطعمة اللي تسبب لجسمك رد فعل تحسسي، مثل الحليب، البيض، المكسرات وغيرها… ويساعدك تتجنبها وتحسّن من صحتك الهضمية والمناعية.
@@ -1289,10 +1294,10 @@
     <t>فحص الزواج للسعوديين</t>
   </si>
   <si>
-    <t>تشمل باقة فحص الزواج للسعوديين تحاليل الكبد الوبائي ب و سي و فايروس نقص المناعة المكتسبة:</t>
-  </si>
-  <si>
-    <t>تشمل باقة فحص الزواج للسعوديين تحاليل الكبد الوبائي ب و سي و فايروس نقص المناعة المكتسبة: تكشف لك عن الفيروسات المعدية التي تنتقل جنسيا او عن طريق الدم. الهيموجلوبين الكهربائي: لكشف عن انواع فقر الدم الوراثي كالثلاسيميا و الأنيميا المنجلية. الزهري: احد الامراض الناتجة عن عدوى فيروسية و التي تنتقل جنسيا. تحليل نازعة هيدروجين: تحليل لقياس نسبة انزيم معين يؤثر على تركيب كريات الدم الحمراء و بالتالي يكون مسؤول عن نوع من انواع فقر الدم و يسمى انيميا الفول. وايضا لدينا باقة فحص الزواج لغير السعوديين
+    <t xml:space="preserve">تشمل باقة فحص الزواج للسعوديين تحاليل الكبد الوبائي ب و سي و فايروس نقص المناعة المكتسبة: تكشف لك عن الفيروسات المعدية التي تنتقل جنسيا او عن طريق الدم. الهيموجلوبين الكهربائي: لكشف عن انواع فقر الدم الوراثي كالثلاسيميا و الأنيميا المنجلية. </t>
+  </si>
+  <si>
+    <t>تشمل التالي : الزهري: احد الامراض الناتجة عن عدوى فيروسية و التي تنتقل جنسيا. تحليل نازعة هيدروجين: تحليل لقياس نسبة انزيم معين يؤثر على تركيب كريات الدم الحمراء و بالتالي يكون مسؤول عن نوع من انواع فقر الدم و يسمى انيميا الفول. وايضا لدينا باقة فحص الزواج لغير السعوديين
 إلیك تفاصیل التحالیل التي تشملھا باقة فحص الزواج للسعوديين
 فيروس نقص المناعه المكتسبة :
 يتم جمع عينة من الدم للبحث عن وجود الأجسام المضاده لفيروس HIV
@@ -1317,10 +1322,10 @@
     <t>باقه الصداع</t>
   </si>
   <si>
-    <t>تحلل أسباب الصداع المتكرر مثل فقر الدم أو اضطرابات الغدة أو نقص الفيتامينات.</t>
-  </si>
-  <si>
-    <t>تحلل أسباب الصداع المتكرر مثل فقر الدم أو اضطرابات الغدة أو نقص الفيتامينات. تساعدك على فهم جذور الألم ووضع خطة علاج فعالة
+    <t>تحلل أسباب الصداع المتكرر مثل فقر الدم أو اضطرابات الغدة أو نقص الفيتامينات. تساعدك على فهم جذور الألم ووضع خطة علاج فعالة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل التحاليل التي تشملها الصداع:
  - صورة الدم الكاملة (CBC):
 تقيّم هذه التحاليل مكونات الدم، بما في ذلك الكريات البيضاء والحمراء والصفائح الدموية، وتقدم معلومات حول الحالة الصحية العامة وكشف الاضطرابات مثل الأنيميا والعدوى.
@@ -1360,10 +1365,10 @@
     <t>باقه تحاليل الاكتياب</t>
   </si>
   <si>
-    <t>تحتوي باقة تحاليل الاكتئاب على فحص المؤشرات الحيوية المرتبطة بالمزاج مثل فيتامين د والهرمونات ، تعزز فهمك للحالة النفسية وتدعمك بخطوة أولى نحو التوازن تفاصيل التحاليل التي تشملها…</t>
-  </si>
-  <si>
-    <t>تحتوي باقة تحاليل الاكتئاب على فحص المؤشرات الحيوية المرتبطة بالمزاج مثل فيتامين د والهرمونات ، تعزز فهمك للحالة النفسية وتدعمك بخطوة أولى نحو التوازن
+    <t>تحتوي باقة تحاليل الاكتئاب على فحص المؤشرات الحيوية المرتبطة بالمزاج مثل فيتامين د والهرمونات ، تعزز فهمك للحالة النفسية وتدعمك بخطوة أولى نحو التوازن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل التحاليل التي تشملها باقة الاكتئاب :
 – صورة الدم الكاملة (CBC):
 يقيس عدد وأنواع خلايا الدم المختلفة، بما في ذلك خلايا الدم الحمراء، البيضاء والصفائح الدموية. ويمكن أن يكشف عن فقر الدم، العدوى، وأمراض الدم الأخرى.
@@ -1402,7 +1407,7 @@
     <t>تحليل حساسية القمح والجلوتين المتقدم هو فحص تشخيصي موسع يشمل فحص السيلياك (الغلوتين) ويضيف مؤشرات مناعية متقدمة لتشخيص أكثر دقة، سواء للحالات المبكرة أو غير الكلاسيكية.</t>
   </si>
   <si>
-    <t>تحليل حساسية القمح والجلوتين المتقدم هو فحص تشخيصي موسع يشمل فحص السيلياك (الغلوتين) ويضيف مؤشرات مناعية متقدمة لتشخيص أكثر دقة، سواء للحالات المبكرة أو غير الكلاسيكية.
+    <t>و تشمل التالي : 
 ما هو تحليل اضطراب الجلوتين وحساسية القمح ( تحليل حساسية القمح المتقدم )؟
 هو تحليل دم متطور يقيس مجموعة واسعة من الأجسام المضادة المرتبطة بتفاعل الجهاز المناعي مع الجلوتين وإنزيمات الجسم المرتبطة به.
 يُستخدم لتشخيص:
@@ -1473,10 +1478,10 @@
     <t>باقه حساسيه المستنشقات</t>
   </si>
   <si>
-    <t>باقة حساسية المستنشقات موجهة للأشخاص الذين يعانون من أعراض تحسسية متكررة مثل العطاس، انسداد الأنف، السعال أو ضيق التنفس.</t>
-  </si>
-  <si>
-    <t>باقة حساسية المستنشقات موجهة للأشخاص الذين يعانون من أعراض تحسسية متكررة مثل العطاس، انسداد الأنف، السعال أو ضيق التنفس. تساعد الباقة في تحديد المواد المستنشقة المسببة للحساسية مثل الغبار، حبوب اللقاح، وبر الحيوانات وغيرها، مما يسهل على المريض والطبيب وضع خطة علاجية مناسبة وتجنب مسببات الحساسية المزيد من التفاصيل
+    <t>باقة حساسية المستنشقات موجهة للأشخاص الذين يعانون من أعراض تحسسية متكررة مثل العطاس، انسداد الأنف، السعال أو ضيق التنفس. تساعد الباقة في تحديد المواد المستنشقة المسببة للحساسية مثل الغبار، حبوب اللقاح، وبر الحيوانات وغيرها، مما يسهل على المريض والطبيب وضع خطة علاجية مناسبة وتجنب مسببات الحساسية</t>
+  </si>
+  <si>
+    <t>اليك المزيد من التفاصيل
 حساسية المستنشقات (38 عنصر) – Allergens specific IgE screening (Inhalant panel):
 فحص شامل لعدد 38 مادة شائعة في البيئة يمكن أن تسبب رد فعل تحسسي عند بعض الأشخاص. يقيس الفحص الأجسام المضادة من نوع IgE الخاصة بالحساسية</t>
   </si>
@@ -1490,10 +1495,10 @@
     <t>تحليل الحديد الغير مرتبط تحليل تشبع الحديد في الدم</t>
   </si>
   <si>
-    <t>تحليل الحديد الغير مرتبط هو فحص دم يساعد في قياس كمية الحديد التي يمكن أن يرتبط بها الدم بعد استخدام الحديد الموجود فعليًا في الجسم.</t>
-  </si>
-  <si>
-    <t>تحليل الحديد الغير مرتبط هو فحص دم يساعد في قياس كمية الحديد التي يمكن أن يرتبط بها الدم بعد استخدام الحديد الموجود فعليًا في الجسم. هذا التحليل مهم للكشف عن نقص الحديد أو زيادته ومتابعة فعالية العلاج بالمكملات الحديدية
+    <t>تحليل الحديد الغير مرتبط هو فحص دم يساعد في قياس كمية الحديد التي يمكن أن يرتبط بها الدم بعد استخدام الحديد الموجود فعليًا في الجسم. هذا التحليل مهم للكشف عن نقص الحديد أو زيادته ومتابعة فعالية العلاج بالمكملات الحديدية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية التحليل
 تشخيص فقر الدم الناتج عن نقص الحديد.
 معرفة سبب التعب المستمر أو الإرهاق.
@@ -1521,14 +1526,14 @@
     <t>تحليل تشبع الحديد بالدم</t>
   </si>
   <si>
-    <t>تحليل تشبع الحديد أو تشبع الترانسفيرين هو فحص دم يُستخدم لقياس نسبة الحديد المرتبط ببروتين الترانسفيرين المسؤول عن نقله في الجسم.</t>
-  </si>
-  <si>
     <t>تحليل تشبع الحديد أو تشبع الترانسفيرين هو فحص دم يُستخدم لقياس نسبة الحديد المرتبط ببروتين الترانسفيرين المسؤول عن نقله في الجسم. يساعد هذا التحليل في تقييم مخزون الحديد وتشخيص حالات مثل فقر الدم أو زيادة الحديد (داء ترسب الأصبغة الدموي أهمية تحليل تشبع الحديد
 تشخيص فقر الدم الناتج عن نقص الحديد.
 الكشف عن زيادة الحديد التي قد تضر الكبد والقلب والبنكرياس.
 تقييم امتصاص الحديد ومراقبة الأشخاص الذين يتلقون مكملات أو علاج بالحديد.
-متابعة أمراض الدم واضطرابات التغذية.
+متابعة أمراض الدم واضطرابات التغذية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 القيم الطبيعية
 النسبة الطبيعية لتشبع الحديد: بين 20% – 50% تقريبًا.
 أقل من 20% → قد يشير إلى نقص الحديد أو فقر الدم.
@@ -1560,7 +1565,7 @@
     <t>تحليل eGFR يقيم تقديريًا قدرة الكلى على تصفية الدم وإزالة الفضلات، اعتمادًا على كرياتينين الدم والعمر والجنس وأحيانًا العرق، للكشف المبكر عن مشاكل الكلى ومتابعة وظائفها.</t>
   </si>
   <si>
-    <t>تحليل eGFR يقيم تقديريًا قدرة الكلى على تصفية الدم وإزالة الفضلات، اعتمادًا على كرياتينين الدم والعمر والجنس وأحيانًا العرق، للكشف المبكر عن مشاكل الكلى ومتابعة وظائفها.
+    <t xml:space="preserve">
 تفاصيل تحليل eGFR
 ما هو تحليل eGFR؟
 تحليل eGFR (Estimated Glomerular Filtration Rate) هو فحص يقدّر معدل الترشيح الكبيبي للكلى، أي كمية الدم التي تقوم الكلى بتصفيتها في الدقيقة. يعتمد الفحص على كرياتينين الدم بالإضافة إلى عوامل مثل العمر، الجنس، وأحيانًا العرق، ليعطي تقييمًا دقيقًا لوظائف الكلى بشكل غير مباشر.
@@ -1595,10 +1600,10 @@
     <t>تحليل معدل انزيمات الكبد</t>
   </si>
   <si>
-    <t>تحليل معدل انزيمات الكبد :</t>
-  </si>
-  <si>
-    <t>تحليل معدل انزيمات الكبد : تحليل شامل يقيس إنزيمات مختلفة منها الألكالين فوسفاتيز (ALP) وجاما جلوتاميل ترانسفيراز (GGT) تُستخدم لتقييم وظائف الكبد.
+    <t>تحليل معدل انزيمات الكبد : تحليل شامل يقيس إنزيمات مختلفة منها الألكالين فوسفاتيز (ALP) وجاما جلوتاميل ترانسفيراز (GGT) تُستخدم لتقييم وظائف الكبد.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية التحليل
 الكشف المبكر عن أمراض الكبد مثل التهاب الكبد أو تليف الكبد.
 متابعة تأثير الأدوية أو المكملات الغذائية على الكبد.
@@ -1648,12 +1653,13 @@
     <t>تحليل الجلوبين في الدم تحليل الجلوبيولين</t>
   </si>
   <si>
-    <t>تحليل الجلوبين يقيس مستوى بروتينات الجلوبولين في الدم، وهي بروتينات تلعب دورًا أساسيًا في دعم جهاز المناعة ونقل المواد في الجسم.</t>
-  </si>
-  <si>
     <t>تحليل الجلوبين يقيس مستوى بروتينات الجلوبولين في الدم، وهي بروتينات تلعب دورًا أساسيًا في دعم جهاز المناعة ونقل المواد في الجسم. يُستخدم هذا التحليل لتقييم صحة الكبد والكلى، الكشف عن الالتهابات المزمنة، ومراقبة بعض الأمراض المناعية والأورام.
 أهمية تحليل الجلوبين
-دعم جهاز المناعة: الجلوبولين يحتوي على الأجسام المضادة التي تحمي الجسم من العدوى.
+دعم جهاز المناعة: الجلوبولين يحتوي على الأجسام المضادة التي تحمي الجسم من العدوى.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+تشمل التالي  :
 مراقبة صحة الكبد والكلى: تساعد مستويات الجلوبولين في الكشف عن مشاكل الكبد والكلى المزمنة.
 تشخيص أمراض الدم والمناعة: بعض الأمراض مثل المايلوما المتعددة واضطرابات المناعة تؤثر على نسبة الجلوبولين.
 متابعة الالتهابات المزمنة: الالتهابات المزمنة قد تؤدي إلى زيادة مستويات الجلوبولين.
@@ -1680,10 +1686,10 @@
     <t>تحليل معدل البروتينات الجزيي في الدم</t>
   </si>
   <si>
-    <t>تحليل معدل البروتينات الجزئي هو فحص دم يقيس أنواع البروتينات المختلفة في الدم، مثل الألبومين والغلوبولين، ويُستخدم لتشخيص ومتابعة العديد من الحالات الصحية مثل الالتهابات، أمراض…</t>
-  </si>
-  <si>
-    <t>تحليل معدل البروتينات الجزئي هو فحص دم يقيس أنواع البروتينات المختلفة في الدم، مثل الألبومين والغلوبولين، ويُستخدم لتشخيص ومتابعة العديد من الحالات الصحية مثل الالتهابات، أمراض الكبد والكلى، واضطرابات الجهاز المناعي.
+    <t>تحليل معدل البروتينات الجزئي هو فحص دم يقيس أنواع البروتينات المختلفة في الدم، مثل الألبومين والغلوبولين، ويُستخدم لتشخيص ومتابعة العديد من الحالات الصحية مثل الالتهابات، أمراض الكبد والكلى، واضطرابات الجهاز المناعي.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية تحليل معدل البروتينات الجزئي
 تشخيص أمراض الكبد: يساعد على الكشف عن مشاكل في إنتاج البروتينات الأساسية.
 مراقبة صحة الكلى: فقدان بعض البروتينات عبر البول قد يشير إلى مشاكل كلوية.
@@ -1714,10 +1720,10 @@
     <t>تحليل الالبومين تحليل الالبومين في الدم</t>
   </si>
   <si>
-    <t>الألبومين هو بروتين أساسي يُنتج في الكبد، يلعب دورًا مهمًا في نقل المواد الغذائية والهرمونات والأدوية، والحفاظ على توازن السوائل في الجسم.</t>
-  </si>
-  <si>
-    <t>الألبومين هو بروتين أساسي يُنتج في الكبد، يلعب دورًا مهمًا في نقل المواد الغذائية والهرمونات والأدوية، والحفاظ على توازن السوائل في الجسم. تحليل الألبومين يساعد على تقييم صحة الكبد والكلى، اكتشاف سوء التغذية، ومراقبة الالتهابات المزمنة
+    <t>الألبومين هو بروتين أساسي يُنتج في الكبد، يلعب دورًا مهمًا في نقل المواد الغذائية والهرمونات والأدوية، والحفاظ على توازن السوائل في الجسم. تحليل الألبومين يساعد على تقييم صحة الكبد والكلى، اكتشاف سوء التغذية، ومراقبة الالتهابات المزمنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية تحليل الألبومين
 تقييم وظائف الكبد: انخفاض الألبومين قد يشير إلى أمراض الكبد المزمنة مثل التليف أو التهاب الكبد.
 مراقبة صحة الكلى: فقدان البروتين عبر البول في أمراض الكلى المزمنة يسبب انخفاض الألبومين.
@@ -1746,10 +1752,10 @@
     <t>تحليل الاميليز amylase للبنكرياس تحليل الاميليز للبنكرياس</t>
   </si>
   <si>
-    <t>تحليل الأميليز هو فحص دم أو بول يقيس مستوى إنزيم الأميليز، وهو إنزيم يُفرز بشكل رئيسي من البنكرياس والغدد اللعابية، ويساعد على هضم النشويات لماذا نحتاج لتحليل الأميليز؟</t>
-  </si>
-  <si>
-    <t>تحليل الأميليز هو فحص دم أو بول يقيس مستوى إنزيم الأميليز، وهو إنزيم يُفرز بشكل رئيسي من البنكرياس والغدد اللعابية، ويساعد على هضم النشويات
+    <t>تحليل الأميليز هو فحص دم أو بول يقيس مستوى إنزيم الأميليز، وهو إنزيم يُفرز بشكل رئيسي من البنكرياس والغدد اللعابية، ويساعد على هضم النشويات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 لماذا نحتاج لتحليل الأميليز؟
 تشخيص التهابات البنكرياس الحادة أو المزمنة
 متابعة حالات حصوات المرارة
@@ -1780,10 +1786,10 @@
     <t>تحليل lipase تحليل وظيفه البنكرياس 2</t>
   </si>
   <si>
-    <t>تحليل Lipase يقيس مستوى إنزيم الليباز في الدم، المسؤول عن هضم الدهون.</t>
-  </si>
-  <si>
-    <t>تحليل Lipase يقيس مستوى إنزيم الليباز في الدم، المسؤول عن هضم الدهون. ارتفاعه غالبًا يشير إلى مشاكل في البنكرياس مثل الالتهاب الحاد أو المزمن، ويعد أداة مهمة لتشخيص وعلاج أمراض الجهاز الهضمي /تفاصيل تحليل Lipase:
+    <t>تحليل Lipase يقيس مستوى إنزيم الليباز في الدم، المسؤول عن هضم الدهون. ارتفاعه غالبًا يشير إلى مشاكل في البنكرياس مثل الالتهاب الحاد أو المزمن، ويعد أداة مهمة لتشخيص وعلاج أمراض الجهاز الهضمي</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تفاصيل تحليل Lipase:
 وظيفة الليباز:
 يساعد على تحليل الدهون وتحويلها إلى أحماض دهنية وجليسرول.
 يعمل بالتعاون مع إنزيمات أخرى مثل الأميلاز والبروتياز لهضم الطعام بشكل كامل.
@@ -1812,12 +1818,12 @@
     <t>تحليل كاشف اورام البنكرياس تحليل كاشف اورام البنكرياس</t>
   </si>
   <si>
-    <t>تحليل كاشف أورام البنكرياس هو فحص دم يُستخدم للكشف عن وجود أورام البنكرياس أو خلايا سرطانية مبكرًا.</t>
-  </si>
-  <si>
     <t>تحليل كاشف أورام البنكرياس هو فحص دم يُستخدم للكشف عن وجود أورام البنكرياس أو خلايا سرطانية مبكرًا. يساعد هذا التحليل الأطباء في تشخيص المرض بشكل أسرع ومتابعة فعالية العلاج لمن تم تشخيصهم بالفعل
 تفاصيل تحليل كاشف أورام البنكرياس
-يتم إجراء التحليل عن طريق سحب عينة دم من الوريد وفحصها في المختبر للكشف عن المؤشرات البيولوجية المرتبطة بأورام البنكرياس مثل CA 19-9. عادة لا يحتاج المريض للصيام، ولكن يجب إبلاغ الطبيب عن أي أدوية أو حالات صحية قد تؤثر على النتائج.
+يتم إجراء التحليل عن طريق سحب عينة دم من الوريد وفحصها في المختبر للكشف عن المؤشرات البيولوجية المرتبطة بأورام البنكرياس مثل CA 19-9. عادة لا يحتاج المريض للصيام، ولكن يجب إبلاغ الطبيب عن أي أدوية أو حالات صحية قد تؤثر على النتائج.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية التحليل
 يساعد التحليل في:
 الكشف المبكر عن أورام البنكرياس قبل ظهور أعراض واضحة.
@@ -1840,10 +1846,10 @@
     <t>تحليل الامراض المناعيه ana test تحليل الامراض المناعيه</t>
   </si>
   <si>
-    <t>تحليل الأمراض المناعية ( تحليل ana ) هو فحص دم متخصص يهدف إلى الكشف عن اضطرابات الجهاز المناعي التي تجعل الجسم يهاجم خلاياه السليمة بدلًا من مقاومة العدوى.</t>
-  </si>
-  <si>
-    <t>تحليل الأمراض المناعية ( تحليل ana ) هو فحص دم متخصص يهدف إلى الكشف عن اضطرابات الجهاز المناعي التي تجعل الجسم يهاجم خلاياه السليمة بدلًا من مقاومة العدوى. يساعد هذا الفحص في تشخيص أمراض المناعة الذاتية مثل: الذئبة الحمراء، التهاب المفاصل الروماتويدي، السيلياك، والتصلب المتعدد
+    <t>تحليل الأمراض المناعية ( تحليل ana ) هو فحص دم متخصص يهدف إلى الكشف عن اضطرابات الجهاز المناعي التي تجعل الجسم يهاجم خلاياه السليمة بدلًا من مقاومة العدوى. يساعد هذا الفحص في تشخيص أمراض المناعة الذاتية مثل: الذئبة الحمراء، التهاب المفاصل الروماتويدي، السيلياك، والتصلب المتعدد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية تحليل الأمراض المناعية ( تحليل ana )
 يحدد ما إذا كانت الأعراض مثل آلام المفاصل، الطفح الجلدي، التعب المزمن مرتبطة بخلل مناعي.
 يكشف عن الأجسام المضادة (Autoantibodies) التي يفرزها الجسم ضد نفسه.
@@ -1875,10 +1881,10 @@
     <t>تحليل فيتامين ب1</t>
   </si>
   <si>
-    <t>تحليل فيتامين ب1 (الثيامين) هو فحص دم يهدف إلى قياس مستوى هذا الفيتامين الحيوي في الجسم.</t>
-  </si>
-  <si>
-    <t>تحليل فيتامين ب1 (الثيامين) هو فحص دم يهدف إلى قياس مستوى هذا الفيتامين الحيوي في الجسم. فيتامين ب1 ضروري لإنتاج الطاقة من الطعام، والحفاظ على وظائف الجهاز العصبي والقلب. نقصه قد يؤدي إلى التعب المزمن، ضعف العضلات، ومشاكل عصبية
+    <t>تحليل فيتامين ب1 (الثيامين) هو فحص دم يهدف إلى قياس مستوى هذا الفيتامين الحيوي في الجسم. فيتامين ب1 ضروري لإنتاج الطاقة من الطعام، والحفاظ على وظائف الجهاز العصبي والقلب. نقصه قد يؤدي إلى التعب المزمن، ضعف العضلات، ومشاكل عصبية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل تحليل فيتامين ب1
 يتم التحليل عن طريق سحب عينة دم من الوريد لقياس مستوى الثيامين بدقة. عادة لا يحتاج المريض للصيام، لكن يجب إبلاغ الطبيب بأي أدوية أو مكملات غذائية لأنها قد تؤثر على النتائج.
 أهمية التحليل
@@ -1902,11 +1908,11 @@
     <t>تحليل فيتامين ب2</t>
   </si>
   <si>
-    <t>تحليل فيتامين ب2 يقيس مستوى الفيتامين B2 أو الريبوفلافين في الدم، وهو ضروري لتحويل الغذاء إلى طاقة، دعم صحة الجلد والعينين، وتقوية الجهاز العصبي تفاصيل تحليل فيتامين ب2 تحليل…</t>
-  </si>
-  <si>
     <t>تحليل فيتامين ب2 يقيس مستوى الفيتامين B2 أو الريبوفلافين في الدم، وهو ضروري لتحويل الغذاء إلى طاقة، دعم صحة الجلد والعينين، وتقوية الجهاز العصبي تفاصيل تحليل فيتامين ب2
-تحليل فيتامين ب2 يُجرى عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة. عادة لا يحتاج المريض إلى صيام، لكن يجب إبلاغ الطبيب عن أي أدوية أو مكملات غذائية لأنها قد تؤثر على نتائج التحليل.
+تحليل فيتامين ب2 يُجرى عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة. عادة لا يحتاج المريض إلى صيام، لكن يجب إبلاغ الطبيب عن أي أدوية أو مكملات غذائية لأنها قد تؤثر على نتائج التحليل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية التحليل
 يساعد التحليل في:
 تشخيص نقص أو زيادة فيتامين B2 الذي قد يؤدي إلى التعب، التهابات الفم، تقرحات الجلد، مشاكل الرؤية، واضطرابات الجهاز العصبي.
@@ -1929,10 +1935,10 @@
     <t>تحليل فيتامين ب6</t>
   </si>
   <si>
-    <t>تحليل فيتامين ب6 يقيس مستوى هذا الفيتامين في الدم وهو ضروري لصحة الأعصاب وإنتاج الطاقة ودعم المناعة تفاصيل تحليل فيتامين ب6 تحليل فيتامين ب6 يُجرى عن طريق سحب عينة دم من الوريد…</t>
-  </si>
-  <si>
-    <t>تحليل فيتامين ب6 يقيس مستوى هذا الفيتامين في الدم وهو ضروري لصحة الأعصاب وإنتاج الطاقة ودعم المناعة
+    <t>تحليل فيتامين ب6 هو فحص مخبري يُستخدم لقياس مستوى هذا الفيتامين في الدم، ويُعد ضروريًا لصحة الأعصاب، وإنتاج الطاقة، ودعم جهاز المناعة. يتم إجراء هذا التحليل عن طريق سحب عينة دم من الوريد، ثم فحصها لتحديد ما إذا كانت مستويات فيتامين ب6 ضمن المعدل الطبيعي أو تحتاج إلى تدخل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل تحليل فيتامين ب6
 تحليل فيتامين ب6 يُجرى عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة. عادة لا يحتاج المريض إلى صيام، لكن يجب إبلاغ الطبيب بأي أدوية أو مكملات غذائية لأنها قد تؤثر على دقة النتائج.
 أهمية التحليل
@@ -1949,10 +1955,10 @@
     <t>تحليل الحديد</t>
   </si>
   <si>
-    <t>تحليل الحديد:</t>
-  </si>
-  <si>
-    <t>تحليل الحديد: يقيس مستوى الحديد في الدم، ويساعد في تشخيص الأنيميا وتقييم صحة الدم والوظائف الحيوية
+    <t>تحليل الحديد: يقيس مستوى الحديد في الدم، ويساعد في تشخيص الأنيميا وتقييم صحة الدم والوظائف الحيوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل تحليل الحديد
 هل تشعر بتعب دائم؟ أو صداع متكرر؟ يمكن يكون السبب نقص الحديد.
 هو من التحاليل الأساسية للكشف عن فقر الدم (الأنيميا) الناتج عن نقص الحديد، وهو ضروري لتقييم صحتك العامة، خصوصًا للنساء، والأطفال، والحوامل، وكبار السن.
@@ -1992,10 +1998,10 @@
     <t>تحليل النحاس</t>
   </si>
   <si>
-    <t>تحليل النحاس :</t>
-  </si>
-  <si>
-    <t>تحليل النحاس : يقيس كمية النحاس في الدم. النحاس معدن يساهم في عدة وظائف حيوية بما في ذلك الأيض واستخدام الحديد وتطور الأنسجة العصبية.
+    <t>تحليل النحاس : يقيس كمية النحاس في الدم. النحاس معدن يساهم في عدة وظائف حيوية بما في ذلك الأيض واستخدام الحديد وتطور الأنسجة العصبية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 المزيد من التفاصيل
 ما هو تحليل النحاس (Copper Test) ؟
 تحليل النحاس هو فحص مخبري يُستخدم لقياس مستوى عنصر النحاس في الدم أو البول. يُعد النحاس من العناصر النادرة الأساسية التي يحتاجها الجسم بكميات صغيرة، وهو يلعب دورًا حيويًا في عدة وظائف بيولوجية، مثل إنتاج الطاقة، وصحة الجهاز العصبي، وتكوين الكولاجين، وتعزيز المناعة.
@@ -2045,12 +2051,10 @@
     <t>تحليل فيتامين ب 12</t>
   </si>
   <si>
-    <t>تحليل فيتامين ب12 ” تحليل b12 ” :</t>
-  </si>
-  <si>
-    <t>تحليل فيتامين ب12 ” تحليل b12 ” : يقيس مقدار فيتامين ب12 في الدم، وهو ضروري لتكوين الحمض النووي، الخلايا العصبية وكريات الدم الحمراء وكذلك للوظائف الإدراكية.
-تعريف تحليل b12
-تحليل فيتامين ب12 هو فحص مخبري يُستخدم لقياس تركيز فيتامين B12 في الدم. هذا الفيتامين ضروري لتكوين خلايا الدم الحمراء، والحفاظ على صحة الجهاز العصبي، والمشاركة في إنتاج الحمض النووي (DNA).
+    <t>تحليل فيتامين ب12 (B12) هو فحص مخبري يُستخدم لقياس مستوى هذا الفيتامين في الدم. يُعد فيتامين ب12 ضروريًا لتكوين خلايا الدم الحمراء، والحفاظ على صحة الجهاز العصبي والخلايا العصبية، كما يلعب دورًا مهمًا في إنتاج الحمض النووي (DNA) ودعم الوظائف الإدراكية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 الغرض من تحليل b12 :
 يُطلب هذا التحليل للكشف عن:
 نقص أو زيادة في مستوى فيتامين B12.
@@ -2100,10 +2104,10 @@
     <t>تحليل البصمه الغذاييه فحص عدم التحمل الغذايي</t>
   </si>
   <si>
-    <t>تحليل البصمة الغذائية هو اختبار يساعد في تحديد الأطعمة التي قد تسبب حساسية أو تفاعلات غير مرغوب فيها في الجسم.</t>
-  </si>
-  <si>
-    <t>تحليل البصمة الغذائية هو اختبار يساعد في تحديد الأطعمة التي قد تسبب حساسية أو تفاعلات غير مرغوب فيها في الجسم. يتم عن طريق فحص الدم لمعرفة استجابة جهاز المناعة لبعض الأطعمة، مما يساعد في تحسين النظام الغذائي وتجنب الأطعمة التي قد تؤثر سلبًا على الصحة &gt;&gt; المزيد من التفاصيل
+    <t>تحليل البصمة الغذائية هو اختبار يساعد في تحديد الأطعمة التي قد تسبب حساسية أو تفاعلات غير مرغوب فيها في الجسم. يتم عن طريق فحص الدم لمعرفة استجابة جهاز المناعة لبعض الأطعمة، مما يساعد في تحسين النظام الغذائي وتجنب الأطعمة التي قد تؤثر سلبًا على الصحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المزيد من التفاصيل
 ما هو تحليل البصمة الغذائية؟
 هو فحص متقدم يهدف إلى تحديد الأطعمة التي قد تُسبب للجسم استجابة مناعية غير طبيعية أو نوعًا من عدم التحمل الغذائي (Food Intolerance).
 يُظهر هذا التحليل كيف يتفاعل جهازك المناعي مع أنواع معينة من الأطعمة عن طريق قياس الأجسام المضادة من نوع IgG في الدم.
@@ -2154,7 +2158,10 @@
     <t>تحليل معدل البروتينات الجزيي في الدم تحليل معدل البروتينيات الحزيي</t>
   </si>
   <si>
-    <t>تحليل معدل البروتينات الجزئي هو فحص دم يقيس أنواع البروتينات المختلفة في الدم، مثل الألبومين والغلوبولين، ويُستخدم لتشخيص ومتابعة العديد من الحالات الصحية مثل الالتهابات، أمراض الكبد والكلى، واضطرابات الجهاز المناعي. أهمية تحليل معدل البروتينات الجزئي
+    <t xml:space="preserve">تحليل معدل البروتينات الجزئي هو فحص دم يقيس أنواع البروتينات المختلفة في الدم، مثل الألبومين والغلوبولين، ويُستخدم لتشخيص ومتابعة العديد من الحالات الصحية مثل الالتهابات، أمراض الكبد والكلى، واضطرابات الجهاز المناعي. </t>
+  </si>
+  <si>
+    <t>أهمية تحليل معدل البروتينات الجزئي
 تشخيص أمراض الكبد: يساعد على الكشف عن مشاكل في إنتاج البروتينات الأساسية.
 مراقبة صحة الكلى: فقدان بعض البروتينات عبر البول قد يشير إلى مشاكل كلوية.
 الكشف عن أمراض المناعة: بعض الأمراض مثل المايلوما المتعددة أو الاضطرابات المناعية المزمنة تؤثر على نسب الغلوبولين.
@@ -2181,14 +2188,16 @@
     <t>تحليل فيتامين ب 2</t>
   </si>
   <si>
+    <t>تحليل فيتامين ب2 (الريبوفلافين) هو فحص مخبري يُستخدم لقياس مستوى هذا الفيتامين في الدم. يُعد ضروريًا لتحويل الغذاء إلى طاقة، ودعم صحة الجلد والعينين، وتعزيز وظائف الجهاز العصبي. يتم إجراء هذا التحليل عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة، وعادة لا يتطلب صيامًا، لكن يُنصح بإبلاغ الطبيب عن أي أدوية أو مكملات غذائية قد تؤثر على النتائج.</t>
+  </si>
+  <si>
     <t>تحليل فيتامين ب 6</t>
   </si>
   <si>
-    <t>تحليل فيتامين ب6 يقيس مستوى هذا الفيتامين في الدم وهو ضروري لصحة الأعصاب وإنتاج الطاقة ودعم المنا تفاصيل تحليل فيتامين ب6 تحليل فيتامين ب6 يُجرى عن طريق سحب عينة دم من الوريد لفحص…</t>
-  </si>
-  <si>
-    <t>تحليل فيتامين ب6 يقيس مستوى هذا الفيتامين في الدم وهو ضروري لصحة الأعصاب وإنتاج الطاقة ودعم المنا تفاصيل تحليل فيتامين ب6
-تحليل فيتامين ب6 يُجرى عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة. عادة لا يحتاج المريض إلى صيام، لكن يجب إبلاغ الطبيب بأي أدوية أو مكملات غذائية لأنها قد تؤثر على دقة النتائج.
+    <t>تحليل فيتامين ب6 هو فحص مخبري يُستخدم لقياس مستوى هذا الفيتامين في الدم، ويُعد ضروريًا لصحة الأعصاب، وإنتاج الطاقة، ودعم جهاز المناعة. يتم إجراء التحليل عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة، وعادة لا يتطلب صيامًا، لكن يُنصح بإبلاغ الطبيب عن أي أدوية أو مكملات غذائية قد تؤثر على دقة النتائج.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 أهمية التحليل
 يساعد التحليل على تشخيص نقص أو زيادة فيتامين ب6 الذي يؤثر على وظائف الجسم المختلفة. النقص قد يؤدي إلى التعب المزمن، ضعف التركيز، اضطرابات المزاج، التنميل أو مشاكل عصبية، في حين أن الزيادة الناتجة عن مكملات بجرعات عالية قد تسبب مشاكل عصبية وحسية.
 متى يطلب الطبيب التحليل؟
@@ -2201,41 +2210,7 @@
 عة</t>
   </si>
   <si>
-    <t>تحليل الحديد: يقيس مستوى الحديد في الدم، ويساعد في تشخيص الأنيميا وتقييم صحة الدم والوظائف الحيوي ة
-تفاصيل تحليل الحديد
-هل تشعر بتعب دائم؟ أو صداع متكرر؟ يمكن يكون السبب نقص الحديد.
-هو من التحاليل الأساسية للكشف عن فقر الدم (الأنيميا) الناتج عن نقص الحديد، وهو ضروري لتقييم صحتك العامة، خصوصًا للنساء، والأطفال، والحوامل، وكبار السن.
-ما هو تحليل الحديد؟
-هو فحص مخبري يُستخدم لقياس:
-مستوى الحديد في الدم
-مخزون الحديد (Ferritin)
-وأحيانًا: تشبع الترانسفرين (Transferrin Saturation)
-يُطلب التحليل عادةً ضمن مجموعة اختبارات فقر الدم (Anaemia Panel).
-متى تحتاج تعمل تحليل الحديد؟
-ينصح الطبيب بعمل التحليل في الحالات التالية:
-التعب العام أو الإرهاق المستمر
-تساقط الشعر وضعف الأظافر
-شحوب البشرة
-الدوخة أو ضيق التنفس
-النساء أثناء الحمل أو الدورة الشهرية الشديدة
-سوء التغذية أو أمراض الجهاز الهضمي
-أنواع تحليل الحديد المتوفرة في مختبرات وريد:
-نوع التحليل
-وصف مختصر
-Iron Serum
-يقيس كمية الحديد في الدم مباشرةً.
-Ferritin
-يقيس مخزون الحديد في الجسم.
-TIBC
-يوضح قدرة الدم على حمل الحديد.
-Transferrin Saturation
-يوضح النسبة المئوية للحديد المرتبط بالترانسفرين.
-هل ممكن أعمل تحليل الحديد من المنزل؟
-نعم، في مختبرات وريد، نوفر سحب عينات من المنزل في أكثر من 50 فرع داخل المملكة.
-فريق متخصص يزورك في منزلك لأخذ العينة، والنتائج تصلك إلكترونيًا خلال ساعات.
-كيف أستعد لتحليل الحديد؟
-يفضل الصيام لمدة 8 ساعات (لكن ليس ضروريًا دائمًا).
-أخبر الفريق الطبي إذا كنت تستخدم مكملات حديد أو أدوية تؤثر على التحليل.</t>
+    <t>تحليل الحديد هو فحص مخبري يُستخدم لقياس مستوى الحديد في الدم، ويساعد في تشخيص فقر الدم (الأنيميا)، وتقييم صحة الدم، ومتابعة كفاءة الوظائف الحيوية في الجسم.</t>
   </si>
   <si>
     <t>تحليل السمنة الجينية</t>
@@ -2244,10 +2219,10 @@
     <t>تحليل السمنه الجينيه</t>
   </si>
   <si>
-    <t>تحليل السمنة الجينية هو تحليل علمي متطور يهدف إلى الكشف عن تأثير الجينات الوراثية على احتمالية زيادة الوزن والإصابة بالسمنة.</t>
-  </si>
-  <si>
-    <t>تحليل السمنة الجينية هو تحليل علمي متطور يهدف إلى الكشف عن تأثير الجينات الوراثية على احتمالية زيادة الوزن والإصابة بالسمنة. يعتمد هذا التحليل على دراسة مجموعة من الجينات المرتبطة بتنظيم الشهية، معدل حرق الدهون، وطريقة معالجة الغذاء تحليل السمنة الجينية هو خطوة نحو رعاية صحية مخصصة تتيح لك فهم “خريطة ” جسمك الوراثية وكيفية استخدامها لصالح صحتك المزيد من التفاصيل
+    <t>تحليل السمنة الجينية هو تحليل علمي متطور يهدف إلى الكشف عن تأثير الجينات الوراثية على احتمالية زيادة الوزن والإصابة بالسمنة. يعتمد هذا التحليل على دراسة مجموعة من الجينات المرتبطة بتنظيم الشهية، معدل حرق الدهون، وطريقة معالجة الغذاء تحليل السمنة الجينية هو خطوة نحو رعاية صحية مخصصة تتيح لك فهم “خريطة ” جسمك الوراثية وكيفية استخدامها لصالح صحتك</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المزيد من التفاصيل
 ما هو تحليل السمنة الجينية؟
 هو فحص متقدم يتم من خلاله دراسة الجينات المرتبطة بزيادة الوزن والسمنة. يعتمد هذا التحليل على فحص الحمض النووي (DNA) للكشف عن التغيرات الجينية التي قد تؤثر على:
 معدل حرق السعرات الحرارية (الأيض)
@@ -2293,10 +2268,10 @@
     <t>تحليل السكر التراكمي</t>
   </si>
   <si>
-    <t>تحليل السكر التراكمي :</t>
-  </si>
-  <si>
-    <t>تحليل السكر التراكمي : هو اختبار يستخدم بشكل رئيسي لمراقبة وإدارة مرض السكري. يعطي هذا الاختبار فكرة عن مستوى الجلوكوز (السكر) في الدم على مدى فترة طويلة، وتحديداً خلال الثلاثة أشهر الماضية، وذلك من خلال قياس نسبة السكر التي ترتبط بالهيموغلوبين داخل كريات الدم الحمراء.
+    <t>تحليل السكر التراكمي : هو اختبار يستخدم بشكل رئيسي لمراقبة وإدارة مرض السكري. يعطي هذا الاختبار فكرة عن مستوى الجلوكوز (السكر) في الدم على مدى فترة طويلة، وتحديداً خلال الثلاثة أشهر الماضية، وذلك من خلال قياس نسبة السكر التي ترتبط بالهيموغلوبين داخل كريات الدم الحمراء.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 المزيد من التفاصيل
 ما هو تحليل السكر التراكمي؟
 تحليل السكر التراكمي، المعروف أيضاً بـ HbA1c، هو اختبار دم يقيس متوسط نسبة السكر في الدم خلال فترة تتراوح بين 2 إلى 3 أشهر الماضية. يختلف هذا التحليل عن فحص السكر العادي الذي يقيس مستوى السكر في وقت معين فقط.
@@ -2324,10 +2299,10 @@
     <t>تحليل الفسفور</t>
   </si>
   <si>
-    <t>تحليل الفسفور :</t>
-  </si>
-  <si>
-    <t>تحليل الفسفور : يقيس مستوى الفسفور في الدم، ويعتبر الفسفور معدناً أساسياً لبناء العظام والأسنان وأيضاً يلعب دوراً في كيفية استخدام الجسم للكربوهيدرات والدهون. كما أنه ضروري لتصنيع البروتين للنمو والترميم والحفاظ على الأنسجة والخلايا. المزيد من التفاصيل
+    <t>تحليل الفسفور : يقيس مستوى الفسفور في الدم، ويعتبر الفسفور معدناً أساسياً لبناء العظام والأسنان وأيضاً يلعب دوراً في كيفية استخدام الجسم للكربوهيدرات والدهون. كما أنه ضروري لتصنيع البروتين للنمو والترميم والحفاظ على الأنسجة والخلايا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المزيد من التفاصيل
 ما هو تحليل الفسفور؟
 هو فحص دم يُستخدم لقياس مستوى عنصر الفسفور (Phosphorus) في الجسم، وهو من المعادن المهمة لصحة العظام والأسنان، ويلعب دورًا في إنتاج الطاقة ووظائف العضلات والأعصاب.
 لماذا يُطلب تحليل الفسفور؟
@@ -2366,10 +2341,10 @@
     <t>تحليل nifty gender</t>
   </si>
   <si>
-    <t>تحليل Nifty Gender الجيني هو اختبار غير جراحي ودقيق يهدف إلى تحديد جنس الجنين قبل الولادة باستخدام عينة دم من الأم.</t>
-  </si>
-  <si>
-    <t>تحليل Nifty Gender الجيني هو اختبار غير جراحي ودقيق يهدف إلى تحديد جنس الجنين قبل الولادة باستخدام عينة دم من الأم. يعتمد التحليل على تقنية متقدمة لتسلسل الحمض النووي الجنيني الحر في دم الأم (cfDNA)، مما يوفر نتائج دقيقة وآمنة دون الحاجة لأي تدخل جراحي. تفاصيل التحليل:
+    <t>تحليل Nifty Gender الجيني هو اختبار غير جراحي ودقيق يهدف إلى تحديد جنس الجنين قبل الولادة باستخدام عينة دم من الأم. يعتمد التحليل على تقنية متقدمة لتسلسل الحمض النووي الجنيني الحر في دم الأم (cfDNA)، مما يوفر نتائج دقيقة وآمنة دون الحاجة لأي تدخل جراحي.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تفاصيل التحليل:
 الهدف من التحليل:
 تحديد جنس الجنين بدقة عالية قبل الولادة.
 تقديم معلومات آمنة للأبوين حول جنس الطفل دون أي مخاطر على الأم أو الجنين.
@@ -2411,10 +2386,10 @@
     <t>باقه well dna silver</t>
   </si>
   <si>
-    <t>تحليل Well DNA Silver يمنحك فهمًا دقيقًا لجسمك من خلال اللياقة، الصحة، والتغذية.</t>
-  </si>
-  <si>
-    <t>تحليل Well DNA Silver يمنحك فهمًا دقيقًا لجسمك من خلال اللياقة، الصحة، والتغذية. يعتمد على عينات الدم لتقديم توصيات شخصية تساعدك على تحسين أدائك البدني، تعزيز صحتك، واتخاذ قرارات غذائية أفضل.
+    <t>تحليل Well DNA Silver يمنحك فهمًا دقيقًا لجسمك من خلال اللياقة، الصحة، والتغذية. يعتمد على عينات الدم لتقديم توصيات شخصية تساعدك على تحسين أدائك البدني، تعزيز صحتك، واتخاذ قرارات غذائية أفضل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 المزيد من التفاصيل Well DNA Silver :
 الهدف:
 تقييم شامل لجسمك بناءً على اللياقة والصحة والتغذية.
@@ -2455,10 +2430,10 @@
     <t>باقه معامل الخطوره الجينيه لسرطان الثدي</t>
   </si>
   <si>
-    <t>باقة معامل الخطورة الجينية لسرطان الثدي صممت خصيصًا لمساعدتك على اكتشاف ما إذا كنتِ تحملين طفرات جينية مرتبطة بزيادة احتمالية الإصابة بسرطان الثدي المزيد من التفاصيل ما هي أهمية…</t>
-  </si>
-  <si>
-    <t>باقة معامل الخطورة الجينية لسرطان الثدي صممت خصيصًا لمساعدتك على اكتشاف ما إذا كنتِ تحملين طفرات جينية مرتبطة بزيادة احتمالية الإصابة بسرطان الثدي المزيد من التفاصيل
+    <t>باقة معامل الخطورة الجينية لسرطان الثدي هي مجموعة فحوصات صُممت خصيصًا لمساعدتك على اكتشاف ما إذا كنتِ تحملين طفرات جينية مرتبطة بزيادة احتمالية الإصابة بسرطان الثدي. تتيح هذه الباقة تقييم مستوى الخطورة لديكِ بشكل مبكر، مما يساعد على اتخاذ إجراءات وقائية مناسبة، مثل المتابعة الدورية أو الفحوصات المبكرة، للحفاظ على صحتك وتقليل المخاطر المحتملة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المزيد من التفاصيل
 ما هي أهمية باقة معامل الخطورة الجينية لسرطان الثدي؟
 باقة معامل الخطورة الجينية لسرطان الثدي صممت خصيصًا لمساعدتك على اكتشاف ما إذا كنتِ تحملين طفرات جينية مرتبطة بزيادة احتمالية الإصابة بسرطان الثدي، مثل الطفرات في جيني BRCA1 وBRCA2، إلى جانب جينات أخرى مؤثرة.
 من خلال باقة معامل الخطورة الجينية لسرطان الثدي، ستحصلين على تحليل عميق ودقيق يظهر ما إذا كنتِ أكثر عرضة وراثيًا للإصابة بهذا النوع من السرطان. هذا التحليل لا يعني بالضرورة أنكِ ستصابين به، لكنه يمنحك رؤية مبكرة تساعدك على اتخاذ خطوات وقائية مناسبة، مثل الفحص الدوري، تعديلات نمط الحياة، أو استشارة مختصين في الطب الوراثي أو الأورام.
@@ -2467,16 +2442,49 @@
 سواء كنتِ تخططين للفحص بدافع الوقاية أو من أجل الاطمئنان فقط، باقة معامل الخطورة الجينية لسرطان الثدي تمثل خطوة مهمة في تمكين المرأة من الاهتمام بصحتها بمستوى جديد من العمق والدقة</t>
   </si>
   <si>
+    <t xml:space="preserve">تحليل Nifty Gender الجيني هو اختبار غير جراحي ودقيق يهدف إلى تحديد جنس الجنين قبل الولادة باستخدام عينة دم من الأم. يعتمد التحليل على تقنية متقدمة لتسلسل الحمض النووي الجنيني الحر في دم الأم (cfDNA)، مما يوفر نتائج دقيقة وآمنة دون الحاجة لأي تدخل جراحي. </t>
+  </si>
+  <si>
+    <t>تفاصيل التحليل:
+الهدف من التحليل:
+تحديد جنس الجنين بدقة عالية قبل الولادة.
+تقديم معلومات آمنة للأبوين حول جنس الطفل دون أي مخاطر على الأم أو الجنين.
+يمكن دمجه مع اختبارات أخرى للكشف عن بعض الاضطرابات الوراثية عند الرغبة.
+طريقة التحليل:
+نوع العينة: دم الأم.
+الفترة الموصى بها لأخذ العينة: من الأسبوع 10 من الحمل وما بعده.
+مدة النتائج: عادة 7-10 أيام عمل.
+يعتمد على تقنيات Next Generation Sequencing (NGS) لتحليل الحمض النووي الجنيني الحر في دم الأم.
+ما يغطيه التحليل:
+الكشف عن كروموسومات X وY لتحديد جنس الجنين.
+يمكن دمجه مع اختبارات Nifty الأخرى للكشف عن:
+متلازمة داون (Trisomy 21)
+متلازمة إدواردز (Trisomy 18)
+متلازمة باتو (Trisomy 13)
+يقدم النتائج بشكل آمن ودقيق مع نسبة ثقة عالية تصل إلى 99%.
+النتائج والتوصيات:
+تقرير مفصل يوضح جنس الجنين.
+نصائح للأبوين حول متابعة الحمل والخطوات التالية إذا رغبوا في إجراء اختبارات إضافية.
+توجيه استشاري في حال رغبة الأم أو الأسرة في تحاليل إضافية للكشف عن الطفرات الوراثية.
+الفوائد الرئيسية:
+آمن وغير جراحي، بدون أي مخاطر على الأم أو الجنين.
+دقة عالية لتحديد الجنس (أكثر من 99%).
+إمكانية دمجه مع اختبارات وراثية أخرى للكشف المبكر عن الأمراض الوراثية.
+يوفر راحة البال للأبوين ويتيح التخطيط المبكر للحمل والأسرة.
+مدة التحليل:
+مدة التحليل: 7-10 أيام عمل.</t>
+  </si>
+  <si>
     <t>الباقات الجينية التشخيصية</t>
   </si>
   <si>
     <t>فحص ما بعد الزواج الجيني</t>
   </si>
   <si>
-    <t>فحص ما بعد الزواج الجيني يساعد الأزواج على تقييم احتمالية انتقال الأمراض الوراثية للأطفال، وتقديم خيارات وقائية وطبية مبنية على نتائج دقيقة.</t>
-  </si>
-  <si>
-    <t>فحص ما بعد الزواج الجيني يساعد الأزواج على تقييم احتمالية انتقال الأمراض الوراثية للأطفال، وتقديم خيارات وقائية وطبية مبنية على نتائج دقيقة.
+    <t>فحص ما بعد الزواج الجيني هو اختبار يُساعد الأزواج على تقييم احتمالية انتقال الأمراض الوراثية إلى الأطفال، ويُوفر خيارات وقائية وطبية مبنية على نتائج دقيقة، مما يُسهم في اتخاذ قرارات صحية مدروسة للمستقبل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 المزيد من التفاصيل
 تقييم مخاطر الوراثة للأطفال
 من خلال فحص ما بعد الزواج الجيني، يتم تحليل الجينات الوراثية لكلا الزوجين، والتأكد من وجود أو غياب الطفرات الجينية المرتبطة بأمراض وراثية خطيرة أو مزمنة. يُستخدم هذا الفحص لتحديد ما إذا كان هناك خطر فعلي من انتقال الطفرات إلى الأبناء، مما يسمح للأزواج بالاستعداد المبكر أو استشارة مختصين في الطب الوراثي لاتخاذ قرارات مبنية على بيانات دقيقة.
@@ -2490,10 +2498,10 @@
     <t>فحص الزواج الجيني</t>
   </si>
   <si>
-    <t>فحص الزواج الجيني هو خطوة علمية وواعية تساعد الشريكين على فهم التوافق الجيني بينهما، والتأكد من احتمالية انتقال أمراض وراثية إلى الأبناء في المستقبل.</t>
-  </si>
-  <si>
-    <t>فحص الزواج الجيني هو خطوة علمية وواعية تساعد الشريكين على فهم التوافق الجيني بينهما، والتأكد من احتمالية انتقال أمراض وراثية إلى الأبناء في المستقبل.
+    <t>فحص الزواج الجيني هو خطوة علمية وواعية تساعد الشريكين على فهم التوافق الجيني بينهما، وتقييم احتمالية انتقال الأمراض الوراثية إلى الأبناء في المستقبل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 المزيد من التفاصيل
 كيف يكشف فحص الزواج الجيني عن مخاطر الأمراض الوراثية للأجيال القادمة؟
 من خلال فحص الزواج الجيني، يتم تحليل عدد من الجينات المرتبطة بالأمراض الوراثية الشائعة مثل الثلاسيميا، فقر الدم المنجلي، التليف الكيسي، وبعض أمراض التمثيل الغذائي. يوضح التحليل ما إذا كان أحد الشريكين (أو كلاهما) حاملًا لطفرة جينية قد تنتقل إلى الجيل القادم، حتى وإن لم تظهر عليهم أي أعراض حالية.
@@ -2515,10 +2523,10 @@
     <t>تحليل المايكروبيوم</t>
   </si>
   <si>
-    <t>تحليل المايكروبيوم هو فحص دقيق وحديث يقيم توازن البكتيريا والكائنات الدقيقة في الجهاز الهضمي، ويقدّم رؤية شاملة عن صحة الهضم والمناعة ويساعد في تشخيص الاضطرابات ووضع خطة علاجية…</t>
-  </si>
-  <si>
-    <t>تحليل المايكروبيوم هو فحص دقيق وحديث يقيم توازن البكتيريا والكائنات الدقيقة في الجهاز الهضمي، ويقدّم رؤية شاملة عن صحة الهضم والمناعة ويساعد في تشخيص الاضطرابات ووضع خطة علاجية مناسبة.
+    <t>تحليل المايكروبيوم هو فحص دقيق وحديث يقيم توازن البكتيريا والكائنات الدقيقة في الجهاز الهضمي، ويقدّم رؤية شاملة عن صحة الهضم والمناعة ويساعد في تشخيص الاضطرابات ووضع خطة علاجية مناسبة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل تحليل المايكروبيوم
 نوع العينة :
 عينة براز، وأحيانًا يمكن أن يشمل فم أو جلد حسب نوع التحليل.
@@ -2555,10 +2563,10 @@
     <t>تحليل السيبو اختبار التنفس للهيدروجين والميثان</t>
   </si>
   <si>
-    <t>تحليل السيبو (SIBO) هو فحص طبي يكشف زيادة نمو البكتيريا في الأمعاء الدقيقة، والتي قد تسبب انتفاخًا، غازات، اضطرابات في الإخراج، وسوء امتصاص الغذاء، ويساعد في تحديد سبب مشاكل الهضم…</t>
-  </si>
-  <si>
-    <t>تحليل السيبو (SIBO) هو فحص طبي يكشف زيادة نمو البكتيريا في الأمعاء الدقيقة، والتي قد تسبب انتفاخًا، غازات، اضطرابات في الإخراج، وسوء امتصاص الغذاء، ويساعد في تحديد سبب مشاكل الهضم ووضع خطة علاج مناسبة
+    <t>تحليل السيبو (SIBO) هو فحص طبي يكشف زيادة نمو البكتيريا في الأمعاء الدقيقة، والتي قد تسبب انتفاخًا، غازات، اضطرابات في الإخراج، وسوء امتصاص الغذاء، ويساعد في تحديد سبب مشاكل الهضم ووضع خطة علاج مناسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل تحليل السيبو
 يعتمد تحليل السيبو (Small Intestinal Bacterial Overgrowth) غالبًا على اختبار التنفس، حيث يقوم المريض بتناول محلول سكري مخصص، ثم يتم قياس مستويات الهيدروجين والميثان في هواء الزفير على فترات زمنية محددة.
 ارتفاع هذه الغازات يدل على وجود نمو بكتيري غير طبيعي في الأمعاء الدقيقة.
@@ -2615,7 +2623,7 @@
     <t>self_collection_package</t>
   </si>
   <si>
-    <t>تحليل Well DNA Silver يمنحك فهمًا دقيقًا لجسمك من خلال اللياقة، الصحة، والتغذية. يعتمد على عينات الدم لتقديم توصيات شخصية تساعدك على تحسين أدائك البدني، تعزيز صحتك، واتخاذ قرارات غذائية أفضل.المزيد من التفاصيل Well DNA Silver :
+    <t>المزيد من التفاصيل Well DNA Silver :
 الهدف:
 تقييم شامل لجسمك بناءً على اللياقة والصحة والتغذية.
 تحديد نقاط القوة والضعف الوراثية.
@@ -2655,7 +2663,7 @@
     <t>تحليل Well DNA Platinum هو التحليل الأكثر شمولية، يمنحك فهمًا كاملاً لجسمك من خلال اللياقة، الصحة، التغذية، البشرة، الأدوية، والنوم.</t>
   </si>
   <si>
-    <t>تحليل Well DNA Platinum هو التحليل الأكثر شمولية، يمنحك فهمًا كاملاً لجسمك من خلال اللياقة، الصحة، التغذية، البشرة، الأدوية، والنوم.
+    <t xml:space="preserve">
 تفاصيل التحليل:
 الهدف:
 تقييم شامل لجسمك من منظور اللياقة، الصحة، التغذية، البشرة، الأدوية، والنوم.
@@ -2705,10 +2713,10 @@
     <t>باقه well dna gold</t>
   </si>
   <si>
-    <t>تحليل Well DNA Gold يمنحك صورة متكاملة عن جسمك وصحتك، مع التركيز على اللياقة، الصحة، التغذية، والبشرة.</t>
-  </si>
-  <si>
-    <t>تحليل Well DNA Gold يمنحك صورة متكاملة عن جسمك وصحتك، مع التركيز على اللياقة، الصحة، التغذية، والبشرة. يعتمد التحليل على عينات الدم لتقديم توصيات شخصية تساعدك على تحسين أدائك البدني، تعزيز صحتك، تحسين التغذية، والحفاظ على صحة بشرتك.
+    <t>تحليل Well DNA Gold يمنحك صورة متكاملة عن جسمك وصحتك، مع التركيز على اللياقة، الصحة، التغذية، والبشرة. يعتمد التحليل على عينات الدم لتقديم توصيات شخصية تساعدك على تحسين أدائك البدني، تعزيز صحتك، تحسين التغذية، والحفاظ على صحة بشرتك.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 تفاصيل التحليل:
 الهدف:
 تقييم شامل لجسمك من منظور اللياقة، الصحة، التغذية، والبشرة.
@@ -2768,7 +2776,43 @@
     <t>No price</t>
   </si>
   <si>
+    <t>باقة الأمراض المعدية PCR هي باقة شاملة ومتكاملة للكشف المبكر والدقيق عن أهم الأمراض المنقولة جنسيًا.</t>
+  </si>
+  <si>
     <t>Missing from runtime_clean_v3</t>
+  </si>
+  <si>
+    <t>اقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس.</t>
+  </si>
+  <si>
+    <t>باقة تحالیل صحة الغدة الدرقیة ھي مجموعة من الاختبارات والتحالیل التي تھدف إلى تقییم و ظیفة الغدة الدرقیة وتشخیص أي اضطرابات فیھا .</t>
+  </si>
+  <si>
+    <t>باقة تحاليل التهابات الجهاز الهضمي هي مجموعة من الاختبارات المختصة التي تهدف إلى تشخيص وتقييم التهابات الجهاز الهضمي واضطراباته.</t>
+  </si>
+  <si>
+    <t>باقة تحاليل الكشف المبكر عن الأورام للنساء هي مجموعة من الاختبارات المخصصة للكشف المبكر عن وجود أورام في الجهاز الهضمي والكبد والثدي والرحم والبنكرياس.</t>
+  </si>
+  <si>
+    <t>تحليل الحديد:</t>
+  </si>
+  <si>
+    <t>تحليل Nifty Gender الجيني هو اختبار غير جراحي ودقيق يهدف إلى تحديد جنس الجنين قبل الولادة باستخدام عينة دم من الأم.</t>
+  </si>
+  <si>
+    <t>تحليل Well DNA Silver يمنحك فهمًا دقيقًا لجسمك من خلال اللياقة، الصحة، والتغذية.</t>
+  </si>
+  <si>
+    <t>باقة معامل الخطورة الجينية لسرطان الثدي صممت خصيصًا لمساعدتك على اكتشاف ما إذا كنتِ تحملين طفرات جينية مرتبطة بزيادة احتمالية الإصابة بسرطان الثدي المزيد من التفاصيل ما هي أهمية…</t>
+  </si>
+  <si>
+    <t>فحص ما بعد الزواج الجيني يساعد الأزواج على تقييم احتمالية انتقال الأمراض الوراثية للأطفال، وتقديم خيارات وقائية وطبية مبنية على نتائج دقيقة.</t>
+  </si>
+  <si>
+    <t>فحص الزواج الجيني هو خطوة علمية وواعية تساعد الشريكين على فهم التوافق الجيني بينهما، والتأكد من احتمالية انتقال أمراض وراثية إلى الأبناء في المستقبل.</t>
+  </si>
+  <si>
+    <t>تحليل Well DNA Gold يمنحك صورة متكاملة عن جسمك وصحتك، مع التركيز على اللياقة، الصحة، التغذية، والبشرة.</t>
   </si>
   <si>
     <t>Present In Runtime</t>
@@ -2802,7 +2846,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2821,13 +2865,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3316,28 +3353,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3346,118 +3386,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4149,17 +4186,17 @@
       <c r="H2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>44</v>
+      <c r="I2" s="10">
+        <v>185</v>
       </c>
       <c r="J2" s="11">
         <v>185</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N2" s="12">
         <v>1</v>
@@ -4194,28 +4231,28 @@
         <v>39</v>
       </c>
       <c r="E3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>44</v>
+      <c r="I3" s="10">
+        <v>185</v>
       </c>
       <c r="J3" s="11">
         <v>185</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N3" s="12">
         <v>1</v>
@@ -4236,7 +4273,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:19">
+    <row r="4" ht="403.2" spans="1:19">
       <c r="A4">
         <v>5</v>
       </c>
@@ -4250,28 +4287,28 @@
         <v>39</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>54</v>
+      <c r="I4" s="10">
+        <v>79</v>
       </c>
       <c r="J4" s="11">
         <v>79</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N4" s="12">
         <v>1</v>
@@ -4306,28 +4343,28 @@
         <v>39</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>54</v>
+      <c r="I5" s="10">
+        <v>79</v>
       </c>
       <c r="J5" s="11">
         <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N5" s="12">
         <v>1</v>
@@ -4348,7 +4385,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" ht="345.6" spans="1:19">
+    <row r="6" ht="302.4" spans="1:19">
       <c r="A6">
         <v>7</v>
       </c>
@@ -4362,28 +4399,28 @@
         <v>39</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>54</v>
+      <c r="I6" s="10">
+        <v>79</v>
       </c>
       <c r="J6" s="11">
         <v>79</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="12">
         <v>1</v>
@@ -4418,28 +4455,28 @@
         <v>39</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="H7" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="I7" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="J7" s="11">
         <v>79</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N7" s="12">
         <v>1</v>
@@ -4460,7 +4497,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="360" spans="1:19">
+    <row r="8" ht="345.6" spans="1:19">
       <c r="A8">
         <v>9</v>
       </c>
@@ -4474,28 +4511,28 @@
         <v>39</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="J8" s="11">
         <v>179</v>
       </c>
       <c r="K8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N8" s="12">
         <v>1</v>
@@ -4516,7 +4553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" ht="172.8" spans="1:19">
+    <row r="9" ht="158.4" spans="1:19">
       <c r="A9">
         <v>10</v>
       </c>
@@ -4530,28 +4567,28 @@
         <v>39</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="I9" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="J9" s="11">
         <v>227</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N9" s="12">
         <v>1</v>
@@ -4572,7 +4609,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" ht="345.6" spans="1:19">
+    <row r="10" ht="331.2" spans="1:19">
       <c r="A10">
         <v>11</v>
       </c>
@@ -4586,28 +4623,28 @@
         <v>39</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>81</v>
-      </c>
       <c r="I10" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J10" s="11">
         <v>227</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N10" s="12">
         <v>1</v>
@@ -4628,7 +4665,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" ht="144" spans="1:19">
+    <row r="11" ht="129.6" spans="1:19">
       <c r="A11">
         <v>12</v>
       </c>
@@ -4642,31 +4679,31 @@
         <v>39</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="I11" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="J11" s="11">
         <v>297</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N11" s="12">
         <v>1</v>
@@ -4687,7 +4724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" ht="403.2" spans="1:19">
+    <row r="12" ht="374.4" spans="1:19">
       <c r="A12">
         <v>13</v>
       </c>
@@ -4701,28 +4738,28 @@
         <v>39</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="I12" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="J12" s="11">
         <v>527</v>
       </c>
       <c r="K12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N12" s="12">
         <v>1</v>
@@ -4743,7 +4780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" ht="288" spans="1:19">
+    <row r="13" ht="259.2" spans="1:19">
       <c r="A13">
         <v>14</v>
       </c>
@@ -4757,28 +4794,28 @@
         <v>39</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="I13" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="J13" s="11">
         <v>1500</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N13" s="12">
         <v>1</v>
@@ -4799,7 +4836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="144" spans="1:19">
+    <row r="14" ht="115.2" spans="1:19">
       <c r="A14" s="5">
         <v>15</v>
       </c>
@@ -4813,23 +4850,23 @@
         <v>39</v>
       </c>
       <c r="E14" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="H14" s="15" t="s">
         <v>98</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>100</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N14" s="5">
         <v>0</v>
@@ -4845,10 +4882,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" ht="259.2" spans="1:19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" ht="230.4" spans="1:19">
       <c r="A15" s="7">
         <v>16</v>
       </c>
@@ -4862,29 +4899,29 @@
         <v>39</v>
       </c>
       <c r="E15" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="H15" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="I15" s="16" t="s">
         <v>105</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>107</v>
       </c>
       <c r="J15" s="17">
         <v>199</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N15" s="7">
         <v>2</v>
@@ -4896,16 +4933,16 @@
         <v>199</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R15" s="7">
         <v>2</v>
       </c>
       <c r="S15" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" ht="201.6" spans="1:19">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" ht="172.8" spans="1:19">
       <c r="A16" s="7">
         <v>17</v>
       </c>
@@ -4919,29 +4956,29 @@
         <v>39</v>
       </c>
       <c r="E16" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="H16" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="I16" s="16" t="s">
         <v>111</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>113</v>
       </c>
       <c r="J16" s="17">
         <v>199</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L16" s="7"/>
       <c r="M16" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N16" s="7">
         <v>2</v>
@@ -4953,16 +4990,16 @@
         <v>199</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R16" s="7">
         <v>2</v>
       </c>
       <c r="S16" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" ht="216" spans="1:19">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" ht="201.6" spans="1:19">
       <c r="A17" s="7">
         <v>18</v>
       </c>
@@ -4976,29 +5013,29 @@
         <v>39</v>
       </c>
       <c r="E17" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="H17" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="I17" s="16" t="s">
         <v>116</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>118</v>
       </c>
       <c r="J17" s="17">
         <v>499</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N17" s="7">
         <v>2</v>
@@ -5010,13 +5047,13 @@
         <v>499</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R17" s="7">
         <v>2</v>
       </c>
       <c r="S17" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:19">
@@ -5033,28 +5070,28 @@
         <v>39</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="H18" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>122</v>
-      </c>
       <c r="I18" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J18" s="11">
         <v>499</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N18" s="12">
         <v>1</v>
@@ -5089,29 +5126,29 @@
         <v>39</v>
       </c>
       <c r="E19" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="H19" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="I19" s="16" t="s">
         <v>125</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>127</v>
       </c>
       <c r="J19" s="17">
         <v>299</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N19" s="7">
         <v>2</v>
@@ -5123,16 +5160,16 @@
         <v>299</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R19" s="7">
         <v>2</v>
       </c>
       <c r="S19" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" ht="259.2" spans="1:19">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" ht="230.4" spans="1:19">
       <c r="A20" s="7">
         <v>21</v>
       </c>
@@ -5146,29 +5183,29 @@
         <v>39</v>
       </c>
       <c r="E20" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>128</v>
-      </c>
       <c r="H20" s="16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J20" s="17">
         <v>199</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N20" s="7">
         <v>2</v>
@@ -5180,13 +5217,13 @@
         <v>199</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R20" s="7">
         <v>2</v>
       </c>
       <c r="S20" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" ht="331.2" spans="1:19">
@@ -5203,29 +5240,29 @@
         <v>39</v>
       </c>
       <c r="E21" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G21" s="16" t="s">
+      <c r="H21" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="16" t="s">
         <v>125</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>127</v>
       </c>
       <c r="J21" s="17">
         <v>299</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N21" s="7">
         <v>2</v>
@@ -5237,16 +5274,16 @@
         <v>299</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R21" s="7">
         <v>2</v>
       </c>
       <c r="S21" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" ht="216" spans="1:19">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" ht="201.6" spans="1:19">
       <c r="A22">
         <v>23</v>
       </c>
@@ -5260,28 +5297,28 @@
         <v>39</v>
       </c>
       <c r="E22" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="I22" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="J22" s="11">
         <v>1400</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N22" s="12">
         <v>1</v>
@@ -5316,28 +5353,28 @@
         <v>39</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="I23" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>140</v>
       </c>
       <c r="J23" s="11">
         <v>399</v>
       </c>
       <c r="K23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N23" s="12">
         <v>1</v>
@@ -5358,7 +5395,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" ht="201.6" spans="1:19">
+    <row r="24" ht="172.8" spans="1:19">
       <c r="A24" s="7">
         <v>25</v>
       </c>
@@ -5372,29 +5409,29 @@
         <v>39</v>
       </c>
       <c r="E24" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="H24" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="I24" s="16" t="s">
         <v>111</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>113</v>
       </c>
       <c r="J24" s="17">
         <v>199</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N24" s="7">
         <v>2</v>
@@ -5406,16 +5443,16 @@
         <v>199</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R24" s="7">
         <v>2</v>
       </c>
       <c r="S24" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" ht="345.6" spans="1:19">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" ht="316.8" spans="1:19">
       <c r="A25">
         <v>26</v>
       </c>
@@ -5429,28 +5466,28 @@
         <v>39</v>
       </c>
       <c r="E25" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>144</v>
-      </c>
       <c r="I25" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J25" s="11">
         <v>299</v>
       </c>
       <c r="K25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N25" s="12">
         <v>1</v>
@@ -5471,7 +5508,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" ht="216" spans="1:19">
+    <row r="26" ht="187.2" spans="1:19">
       <c r="A26" s="7">
         <v>27</v>
       </c>
@@ -5485,29 +5522,29 @@
         <v>39</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G26" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="16" t="s">
         <v>116</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>118</v>
       </c>
       <c r="J26" s="17">
         <v>499</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N26" s="7">
         <v>2</v>
@@ -5519,16 +5556,16 @@
         <v>499</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R26" s="7">
         <v>2</v>
       </c>
       <c r="S26" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" ht="316.8" spans="1:19">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" ht="273.6" spans="1:19">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5542,31 +5579,31 @@
         <v>39</v>
       </c>
       <c r="E27" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="G27" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="H27" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="I27" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="J27" s="11">
         <v>227</v>
       </c>
       <c r="K27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L27">
         <v>9</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N27" s="12">
         <v>1</v>
@@ -5587,7 +5624,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" ht="273.6" spans="1:19">
+    <row r="28" ht="259.2" spans="1:19">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5601,28 +5638,28 @@
         <v>39</v>
       </c>
       <c r="E28" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="G28" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="H28" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="H28" s="10" t="s">
-        <v>153</v>
-      </c>
       <c r="I28" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J28" s="11">
         <v>499</v>
       </c>
       <c r="K28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N28" s="12">
         <v>1</v>
@@ -5657,28 +5694,28 @@
         <v>39</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>157</v>
-      </c>
       <c r="I29" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J29" s="11">
         <v>299</v>
       </c>
       <c r="K29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N29" s="12">
         <v>1</v>
@@ -5699,7 +5736,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" ht="187.2" spans="1:19">
+    <row r="30" ht="172.8" spans="1:19">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5713,28 +5750,28 @@
         <v>39</v>
       </c>
       <c r="E30" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="G30" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="H30" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="I30" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J30" s="11">
         <v>199</v>
       </c>
       <c r="K30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N30" s="12">
         <v>1</v>
@@ -5755,7 +5792,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" ht="187.2" spans="1:19">
+    <row r="31" ht="172.8" spans="1:19">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5769,28 +5806,28 @@
         <v>39</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="G31" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="10" t="s">
-        <v>165</v>
-      </c>
       <c r="I31" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J31" s="11">
         <v>299</v>
       </c>
       <c r="K31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N31" s="12">
         <v>1</v>
@@ -5811,7 +5848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" ht="259.2" spans="1:19">
+    <row r="32" ht="230.4" spans="1:19">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5825,28 +5862,28 @@
         <v>39</v>
       </c>
       <c r="E32" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="G32" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="10" t="s">
+      <c r="H32" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="I32" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="J32" s="11">
         <v>799</v>
       </c>
       <c r="K32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N32" s="12">
         <v>1</v>
@@ -5867,7 +5904,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="259.2" spans="1:19">
+    <row r="33" ht="230.4" spans="1:19">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5881,28 +5918,28 @@
         <v>39</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="G33" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="I33" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J33" s="11">
         <v>499</v>
       </c>
       <c r="K33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N33" s="12">
         <v>1</v>
@@ -5937,28 +5974,28 @@
         <v>39</v>
       </c>
       <c r="E34" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="G34" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="H34" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="I34" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J34" s="11">
         <v>299</v>
       </c>
       <c r="K34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N34" s="12">
         <v>1</v>
@@ -5979,7 +6016,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" ht="288" spans="1:19">
+    <row r="35" ht="273.6" spans="1:19">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5993,28 +6030,28 @@
         <v>39</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="G35" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="I35" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="J35" s="11">
         <v>149</v>
       </c>
       <c r="K35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N35" s="12">
         <v>1</v>
@@ -6035,7 +6072,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" ht="115.2" spans="1:19">
+    <row r="36" ht="100.8" spans="1:19">
       <c r="A36">
         <v>37</v>
       </c>
@@ -6049,28 +6086,28 @@
         <v>39</v>
       </c>
       <c r="E36" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="G36" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="H36" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="H36" s="10" t="s">
-        <v>186</v>
-      </c>
       <c r="I36" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J36" s="11">
         <v>499</v>
       </c>
       <c r="K36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N36" s="12">
         <v>1</v>
@@ -6105,28 +6142,28 @@
         <v>39</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="G37" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="I37" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J37" s="11">
         <v>399</v>
       </c>
       <c r="K37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N37" s="12">
         <v>1</v>
@@ -6147,7 +6184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" ht="129.6" spans="1:19">
+    <row r="38" ht="115.2" spans="1:19">
       <c r="A38">
         <v>39</v>
       </c>
@@ -6161,28 +6198,28 @@
         <v>39</v>
       </c>
       <c r="E38" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="G38" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="H38" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>194</v>
-      </c>
       <c r="I38" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J38" s="11">
         <v>299</v>
       </c>
       <c r="K38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N38" s="12">
         <v>1</v>
@@ -6203,7 +6240,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" ht="129.6" spans="1:19">
+    <row r="39" ht="115.2" spans="1:19">
       <c r="A39">
         <v>40</v>
       </c>
@@ -6217,28 +6254,28 @@
         <v>39</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="G39" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="I39" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="J39" s="11">
         <v>599</v>
       </c>
       <c r="K39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N39" s="12">
         <v>1</v>
@@ -6259,7 +6296,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" ht="288" spans="1:19">
+    <row r="40" ht="273.6" spans="1:19">
       <c r="A40">
         <v>41</v>
       </c>
@@ -6273,28 +6310,28 @@
         <v>39</v>
       </c>
       <c r="E40" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="G40" s="10" t="s">
+      <c r="H40" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="I40" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="J40" s="11">
         <v>499</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N40" s="12">
         <v>1</v>
@@ -6329,28 +6366,28 @@
         <v>39</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="G41" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H41" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="I41" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J41" s="11">
         <v>399</v>
       </c>
       <c r="K41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N41" s="12">
         <v>1</v>
@@ -6385,28 +6422,28 @@
         <v>39</v>
       </c>
       <c r="E42" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="G42" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="H42" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>211</v>
-      </c>
       <c r="I42" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J42" s="11">
         <v>399</v>
       </c>
       <c r="K42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N42" s="12">
         <v>1</v>
@@ -6441,28 +6478,28 @@
         <v>39</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="G43" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>215</v>
-      </c>
       <c r="I43" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J43" s="11">
         <v>399</v>
       </c>
       <c r="K43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N43" s="12">
         <v>1</v>
@@ -6488,7 +6525,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>38</v>
@@ -6497,34 +6534,34 @@
         <v>39</v>
       </c>
       <c r="E44" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="G44" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="H44" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="I44" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="J44" s="11">
         <v>227</v>
       </c>
       <c r="K44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N44" s="12">
         <v>1</v>
       </c>
       <c r="O44" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P44" s="14">
         <v>227</v>
@@ -6539,48 +6576,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" ht="316.8" spans="1:19">
+    <row r="45" ht="302.4" spans="1:19">
       <c r="A45">
         <v>51</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="F45" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="I45" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="J45" s="11">
         <v>39</v>
       </c>
       <c r="K45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M45" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N45" s="12">
         <v>1</v>
       </c>
       <c r="O45" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P45" s="14">
         <v>39</v>
@@ -6595,48 +6632,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" ht="345.6" spans="1:19">
+    <row r="46" ht="259.2" spans="1:19">
       <c r="A46">
         <v>52</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E46" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="G46" s="10" t="s">
+      <c r="H46" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="I46" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="J46" s="11">
         <v>75</v>
       </c>
       <c r="K46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N46" s="12">
         <v>1</v>
       </c>
       <c r="O46" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P46" s="14">
         <v>75</v>
@@ -6651,48 +6688,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" ht="374.4" spans="1:19">
+    <row r="47" ht="360" spans="1:19">
       <c r="A47">
         <v>53</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="G47" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="I47" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="J47" s="11">
         <v>50</v>
       </c>
       <c r="K47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M47" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N47" s="12">
         <v>1</v>
       </c>
       <c r="O47" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P47" s="14">
         <v>50</v>
@@ -6707,48 +6744,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" ht="374.4" spans="1:19">
+    <row r="48" ht="360" spans="1:19">
       <c r="A48">
         <v>54</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E48" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="F48" s="10" t="s">
-        <v>237</v>
-      </c>
       <c r="G48" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H48" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="I48" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="J48" s="11">
         <v>50</v>
       </c>
       <c r="K48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N48" s="12">
         <v>1</v>
       </c>
       <c r="O48" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P48" s="14">
         <v>50</v>
@@ -6768,43 +6805,43 @@
         <v>57</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="I49" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="J49" s="11">
         <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M49" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N49" s="12">
         <v>1</v>
       </c>
       <c r="O49" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P49" s="14">
         <v>17</v>
@@ -6824,43 +6861,43 @@
         <v>58</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E50" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="G50" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="H50" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="H50" s="10" t="s">
-        <v>245</v>
-      </c>
       <c r="I50" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J50" s="11">
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N50" s="12">
         <v>1</v>
       </c>
       <c r="O50" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P50" s="14">
         <v>17</v>
@@ -6880,43 +6917,43 @@
         <v>59</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F51" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="G51" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="H51" s="10" t="s">
-        <v>249</v>
-      </c>
       <c r="I51" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J51" s="11">
         <v>50</v>
       </c>
       <c r="K51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N51" s="12">
         <v>1</v>
       </c>
       <c r="O51" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P51" s="14">
         <v>50</v>
@@ -6931,48 +6968,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" ht="316.8" spans="1:19">
+    <row r="52" ht="302.4" spans="1:19">
       <c r="A52">
         <v>60</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E52" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="G52" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="H52" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="H52" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="I52" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J52" s="11">
         <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N52" s="12">
         <v>1</v>
       </c>
       <c r="O52" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P52" s="14">
         <v>17</v>
@@ -6987,48 +7024,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" ht="302.4" spans="1:19">
+    <row r="53" ht="288" spans="1:19">
       <c r="A53">
         <v>61</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F53" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="G53" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="I53" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>258</v>
       </c>
       <c r="J53" s="11">
         <v>27</v>
       </c>
       <c r="K53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M53" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N53" s="12">
         <v>1</v>
       </c>
       <c r="O53" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P53" s="14">
         <v>27</v>
@@ -7043,48 +7080,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" ht="316.8" spans="1:19">
+    <row r="54" ht="302.4" spans="1:19">
       <c r="A54">
         <v>62</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E54" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F54" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="G54" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="H54" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="H54" s="10" t="s">
-        <v>262</v>
-      </c>
       <c r="I54" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J54" s="11">
         <v>27</v>
       </c>
       <c r="K54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N54" s="12">
         <v>1</v>
       </c>
       <c r="O54" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P54" s="14">
         <v>27</v>
@@ -7099,48 +7136,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" ht="403.2" spans="1:19">
+    <row r="55" ht="345.6" spans="1:19">
       <c r="A55">
         <v>63</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="F55" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="G55" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="H55" s="10" t="s">
-        <v>266</v>
-      </c>
       <c r="I55" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J55" s="11">
         <v>27</v>
       </c>
       <c r="K55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M55" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N55" s="12">
         <v>1</v>
       </c>
       <c r="O55" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P55" s="14">
         <v>27</v>
@@ -7155,48 +7192,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" ht="388.8" spans="1:19">
+    <row r="56" ht="360" spans="1:19">
       <c r="A56">
         <v>64</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E56" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F56" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="G56" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="H56" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="I56" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="J56" s="11">
         <v>150</v>
       </c>
       <c r="K56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N56" s="12">
         <v>1</v>
       </c>
       <c r="O56" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P56" s="14">
         <v>150</v>
@@ -7211,48 +7248,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" ht="316.8" spans="1:19">
+    <row r="57" ht="302.4" spans="1:19">
       <c r="A57">
         <v>65</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H57" s="10" t="s">
-        <v>274</v>
-      </c>
       <c r="I57" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J57" s="11">
         <v>149</v>
       </c>
       <c r="K57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M57" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N57" s="12">
         <v>1</v>
       </c>
       <c r="O57" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P57" s="14">
         <v>149</v>
@@ -7272,43 +7309,43 @@
         <v>66</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E58" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="G58" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="F58" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="G58" s="10" t="s">
+      <c r="H58" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="H58" s="10" t="s">
-        <v>277</v>
-      </c>
       <c r="I58" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J58" s="11">
         <v>149</v>
       </c>
       <c r="K58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M58" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N58" s="12">
         <v>1</v>
       </c>
       <c r="O58" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" s="14">
         <v>149</v>
@@ -7328,43 +7365,43 @@
         <v>67</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="H59" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="I59" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J59" s="11">
         <v>149</v>
       </c>
       <c r="K59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M59" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N59" s="12">
         <v>1</v>
       </c>
       <c r="O59" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" s="14">
         <v>149</v>
@@ -7384,56 +7421,56 @@
         <v>68</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>38</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E60" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="G60" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="F60" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="G60" s="16" t="s">
+      <c r="H60" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="H60" s="16" t="s">
-        <v>283</v>
-      </c>
       <c r="I60" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J60" s="17">
         <v>17</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L60" s="7"/>
       <c r="M60" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N60" s="7">
         <v>2</v>
       </c>
       <c r="O60" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P60" s="17">
         <v>17</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R60" s="7">
         <v>2</v>
       </c>
       <c r="S60" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" ht="409.5" spans="1:19">
@@ -7441,43 +7478,43 @@
         <v>69</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="H61" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="I61" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J61" s="11">
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M61" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N61" s="12">
         <v>1</v>
       </c>
       <c r="O61" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P61" s="14">
         <v>17</v>
@@ -7497,43 +7534,43 @@
         <v>70</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E62" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="G62" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="F62" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="G62" s="10" t="s">
+      <c r="H62" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="H62" s="10" t="s">
-        <v>289</v>
-      </c>
       <c r="I62" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J62" s="11">
         <v>27</v>
       </c>
       <c r="K62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M62" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N62" s="12">
         <v>1</v>
       </c>
       <c r="O62" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P62" s="14">
         <v>27</v>
@@ -7553,43 +7590,43 @@
         <v>71</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F63" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="G63" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="I63" s="10" t="s">
         <v>293</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="J63" s="11">
         <v>827</v>
       </c>
       <c r="K63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M63" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N63" s="12">
         <v>1</v>
       </c>
       <c r="O63" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P63" s="14">
         <v>827</v>
@@ -7609,43 +7646,43 @@
         <v>72</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E64" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="G64" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>248</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>297</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J64" s="11">
         <v>50</v>
       </c>
       <c r="K64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M64" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N64" s="12">
         <v>1</v>
       </c>
       <c r="O64" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P64" s="14">
         <v>50</v>
@@ -7665,13 +7702,13 @@
         <v>73</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>298</v>
@@ -7680,28 +7717,28 @@
         <v>298</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="H65" s="10" t="s">
-        <v>277</v>
-      </c>
       <c r="I65" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J65" s="11">
         <v>149</v>
       </c>
       <c r="K65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M65" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N65" s="12">
         <v>1</v>
       </c>
       <c r="O65" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P65" s="14">
         <v>149</v>
@@ -7716,48 +7753,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" ht="273.6" spans="1:19">
+    <row r="66" ht="244.8" spans="1:19">
       <c r="A66">
         <v>74</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J66" s="11">
         <v>149</v>
       </c>
       <c r="K66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N66" s="12">
         <v>1</v>
       </c>
       <c r="O66" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P66" s="14">
         <v>149</v>
@@ -7777,56 +7814,56 @@
         <v>75</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>38</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G67" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="H67" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="H67" s="16" t="s">
-        <v>302</v>
-      </c>
       <c r="I67" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J67" s="17">
         <v>17</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N67" s="7">
         <v>2</v>
       </c>
       <c r="O67" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P67" s="17">
         <v>17</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R67" s="7">
         <v>2</v>
       </c>
       <c r="S67" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" ht="409.5" spans="1:19">
@@ -7834,43 +7871,43 @@
         <v>76</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J68" s="11">
         <v>1499</v>
       </c>
       <c r="K68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M68" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N68" s="12">
         <v>1</v>
       </c>
       <c r="O68" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P68" s="14">
         <v>1499</v>
@@ -7885,48 +7922,48 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" ht="409.5" spans="1:19">
+    <row r="69" ht="388.8" spans="1:19">
       <c r="A69">
         <v>77</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J69" s="11">
         <v>27</v>
       </c>
       <c r="K69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M69" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N69" s="12">
         <v>1</v>
       </c>
       <c r="O69" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P69" s="14">
         <v>27</v>
@@ -7946,43 +7983,43 @@
         <v>78</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J70" s="11">
         <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M70" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N70" s="12">
         <v>1</v>
       </c>
       <c r="O70" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P70" s="14">
         <v>17</v>
@@ -7997,37 +8034,37 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" ht="409.5" spans="1:19">
+    <row r="71" ht="403.2" spans="1:19">
       <c r="A71" s="5">
         <v>106</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I71" s="15"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N71" s="5">
         <v>0</v>
@@ -8037,13 +8074,13 @@
       </c>
       <c r="P71" s="5"/>
       <c r="Q71" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R71" s="5">
         <v>2</v>
       </c>
       <c r="S71" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" ht="409.5" spans="1:19">
@@ -8051,32 +8088,32 @@
         <v>107</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I72" s="15"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N72" s="5">
         <v>0</v>
@@ -8086,46 +8123,46 @@
       </c>
       <c r="P72" s="5"/>
       <c r="Q72" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R72" s="5">
         <v>2</v>
       </c>
       <c r="S72" s="15" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="73" ht="187.2" spans="1:19">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="73" ht="172.8" spans="1:19">
       <c r="A73" s="5">
         <v>109</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I73" s="15"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
       <c r="M73" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N73" s="5">
         <v>0</v>
@@ -8141,40 +8178,40 @@
         <v>1</v>
       </c>
       <c r="S73" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="74" ht="409.5" spans="1:19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" ht="403.2" spans="1:19">
       <c r="A74" s="5">
         <v>110</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="I74" s="15"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N74" s="5">
         <v>0</v>
@@ -8184,46 +8221,46 @@
       </c>
       <c r="P74" s="5"/>
       <c r="Q74" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R74" s="5">
         <v>2</v>
       </c>
       <c r="S74" s="15" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="75" ht="201.6" spans="1:19">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="75" ht="187.2" spans="1:19">
       <c r="A75" s="5">
         <v>113</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I75" s="15"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
       <c r="M75" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N75" s="5">
         <v>0</v>
@@ -8239,40 +8276,40 @@
         <v>1</v>
       </c>
       <c r="S75" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="76" ht="187.2" spans="1:19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" ht="172.8" spans="1:19">
       <c r="A76" s="5">
         <v>114</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G76" s="15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I76" s="15"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
       <c r="M76" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N76" s="5">
         <v>0</v>
@@ -8288,51 +8325,51 @@
         <v>1</v>
       </c>
       <c r="S76" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="77" ht="388.8" spans="1:19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" ht="374.4" spans="1:19">
       <c r="A77">
         <v>119</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J77" s="11">
         <v>2800</v>
       </c>
       <c r="K77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M77" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N77" s="12">
         <v>1</v>
       </c>
       <c r="O77" s="13" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="P77" s="14">
         <v>2800</v>
@@ -8352,43 +8389,43 @@
         <v>120</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J78" s="11">
         <v>950</v>
       </c>
       <c r="K78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M78" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N78" s="12">
         <v>1</v>
       </c>
       <c r="O78" s="13" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="P78" s="14">
         <v>950</v>
@@ -8408,32 +8445,32 @@
         <v>121</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="I79" s="15"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
       <c r="M79" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N79" s="5">
         <v>0</v>
@@ -8443,13 +8480,13 @@
       </c>
       <c r="P79" s="5"/>
       <c r="Q79" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R79" s="5">
         <v>2</v>
       </c>
       <c r="S79" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80" ht="409.5" spans="1:19">
@@ -8457,32 +8494,32 @@
         <v>122</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="I80" s="15"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
       <c r="M80" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N80" s="5">
         <v>0</v>
@@ -8498,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="S80" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:19">
@@ -8506,32 +8543,32 @@
         <v>123</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H81" s="15" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I81" s="15"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
       <c r="M81" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N81" s="5">
         <v>0</v>
@@ -8547,7 +8584,7 @@
         <v>1</v>
       </c>
       <c r="S81" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -8582,27 +8619,27 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C2" s="2">
         <v>2</v>
@@ -8622,10 +8659,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
@@ -8668,10 +8705,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -8691,10 +8728,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -8714,10 +8751,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
@@ -8737,10 +8774,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
@@ -8760,7 +8797,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>39</v>
@@ -8783,10 +8820,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C10" s="2">
         <v>26</v>
@@ -8830,7 +8867,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -8848,12 +8885,12 @@
         <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -8862,19 +8899,19 @@
         <v>37</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>99</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B3" s="5">
         <v>15</v>
@@ -8883,19 +8920,19 @@
         <v>37</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>99</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:7">
       <c r="A4" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B4" s="7">
         <v>16</v>
@@ -8904,21 +8941,21 @@
         <v>37</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>105</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="7">
         <v>17</v>
@@ -8927,21 +8964,21 @@
         <v>37</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>111</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" ht="28.8" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" s="7">
         <v>18</v>
@@ -8950,21 +8987,21 @@
         <v>37</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>116</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" ht="28.8" spans="1:7">
       <c r="A7" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B7" s="7">
         <v>20</v>
@@ -8973,21 +9010,21 @@
         <v>37</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="7">
         <v>21</v>
@@ -8996,21 +9033,21 @@
         <v>37</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>128</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B9" s="7">
         <v>22</v>
@@ -9019,21 +9056,21 @@
         <v>37</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7">
         <v>25</v>
@@ -9042,21 +9079,21 @@
         <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>111</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" s="7">
         <v>27</v>
@@ -9065,524 +9102,524 @@
         <v>37</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>116</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B12" s="7">
         <v>68</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>282</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B13" s="7">
         <v>75</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>282</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:7">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B14" s="3">
         <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:7">
       <c r="A15" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B15" s="7">
         <v>106</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B16" s="5">
         <v>106</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B17" s="3">
         <v>107</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" s="7">
         <v>107</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B19" s="5">
         <v>107</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" ht="28.8" spans="1:7">
       <c r="A20" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B20" s="3">
         <v>109</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>329</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" ht="28.8" spans="1:7">
       <c r="A21" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B21" s="5">
         <v>109</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>329</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" ht="28.8" spans="1:7">
       <c r="A22" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B22" s="3">
         <v>110</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" ht="28.8" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B23" s="7">
         <v>110</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" ht="28.8" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B24" s="5">
         <v>110</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" ht="28.8" spans="1:7">
       <c r="A25" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B25" s="3">
         <v>113</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" ht="28.8" spans="1:7">
       <c r="A26" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B26" s="5">
         <v>113</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:7">
       <c r="A27" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B27" s="3">
         <v>114</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" ht="28.8" spans="1:7">
       <c r="A28" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B28" s="5">
         <v>114</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B29" s="3">
         <v>121</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B30" s="7">
         <v>121</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B31" s="5">
         <v>121</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:7">
       <c r="A32" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B32" s="3">
         <v>122</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:7">
       <c r="A33" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B33" s="5">
         <v>122</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:7">
       <c r="A34" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B34" s="3">
         <v>123</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:7">
       <c r="A35" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B35" s="5">
         <v>123</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -9620,19 +9657,19 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9646,7 +9683,7 @@
         <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>
@@ -9666,13 +9703,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>37</v>
@@ -9692,13 +9729,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>37</v>
@@ -9718,13 +9755,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>37</v>
@@ -9744,13 +9781,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -9770,13 +9807,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -9796,13 +9833,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
@@ -9822,13 +9859,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -9848,13 +9885,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>37</v>
@@ -9874,13 +9911,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
@@ -9900,13 +9937,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
         <v>37</v>
@@ -9926,13 +9963,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
         <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
         <v>37</v>
@@ -9952,19 +9989,19 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -9972,13 +10009,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -9990,7 +10027,7 @@
         <v>199</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -9998,13 +10035,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
         <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -10016,7 +10053,7 @@
         <v>199</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -10024,13 +10061,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>
@@ -10042,7 +10079,7 @@
         <v>499</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -10050,13 +10087,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
         <v>37</v>
@@ -10076,13 +10113,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
         <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
         <v>37</v>
@@ -10094,7 +10131,7 @@
         <v>299</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -10102,13 +10139,13 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
         <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
         <v>37</v>
@@ -10120,7 +10157,7 @@
         <v>199</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -10128,13 +10165,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
         <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
         <v>37</v>
@@ -10146,7 +10183,7 @@
         <v>299</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -10154,13 +10191,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
         <v>37</v>
@@ -10180,13 +10217,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
         <v>37</v>
@@ -10206,13 +10243,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
         <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
         <v>37</v>
@@ -10224,7 +10261,7 @@
         <v>199</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -10232,13 +10269,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
         <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
         <v>37</v>
@@ -10258,13 +10295,13 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
         <v>37</v>
@@ -10276,7 +10313,7 @@
         <v>499</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -10284,13 +10321,13 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
         <v>37</v>
@@ -10310,13 +10347,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
         <v>37</v>
@@ -10336,13 +10373,13 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
         <v>37</v>
@@ -10362,13 +10399,13 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
         <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
         <v>37</v>
@@ -10388,13 +10425,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C31" t="s">
         <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
         <v>37</v>
@@ -10414,13 +10451,13 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
         <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
         <v>37</v>
@@ -10440,13 +10477,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C33" t="s">
         <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
         <v>37</v>
@@ -10466,13 +10503,13 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C34" t="s">
         <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
         <v>37</v>
@@ -10492,13 +10529,13 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C35" t="s">
         <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
         <v>37</v>
@@ -10518,13 +10555,13 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
         <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
         <v>37</v>
@@ -10544,13 +10581,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C37" t="s">
         <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
         <v>37</v>
@@ -10570,13 +10607,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s">
         <v>37</v>
@@ -10596,13 +10633,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" t="s">
         <v>37</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
         <v>37</v>
@@ -10622,13 +10659,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C40" t="s">
         <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
         <v>37</v>
@@ -10648,13 +10685,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C41" t="s">
         <v>37</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
         <v>37</v>
@@ -10674,13 +10711,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
         <v>37</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
         <v>37</v>
@@ -10700,13 +10737,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
         <v>37</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
         <v>37</v>
@@ -10726,16 +10763,16 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F44">
         <v>227</v>
@@ -10752,16 +10789,16 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F45">
         <v>39</v>
@@ -10778,16 +10815,16 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F46">
         <v>75</v>
@@ -10804,16 +10841,16 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F47">
         <v>50</v>
@@ -10830,16 +10867,16 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F48">
         <v>50</v>
@@ -10856,16 +10893,16 @@
         <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C49" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F49">
         <v>17</v>
@@ -10882,16 +10919,16 @@
         <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F50">
         <v>17</v>
@@ -10908,16 +10945,16 @@
         <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -10934,16 +10971,16 @@
         <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F52">
         <v>17</v>
@@ -10960,16 +10997,16 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F53">
         <v>27</v>
@@ -10986,16 +11023,16 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F54">
         <v>27</v>
@@ -11012,16 +11049,16 @@
         <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F55">
         <v>27</v>
@@ -11038,16 +11075,16 @@
         <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F56">
         <v>150</v>
@@ -11064,16 +11101,16 @@
         <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F57">
         <v>149</v>
@@ -11090,16 +11127,16 @@
         <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F58">
         <v>149</v>
@@ -11116,16 +11153,16 @@
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F59">
         <v>149</v>
@@ -11142,16 +11179,16 @@
         <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F60">
         <v>17</v>
@@ -11160,7 +11197,7 @@
         <v>17</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -11168,16 +11205,16 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C61" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61">
         <v>17</v>
@@ -11194,16 +11231,16 @@
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F62">
         <v>27</v>
@@ -11220,16 +11257,16 @@
         <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F63">
         <v>827</v>
@@ -11246,16 +11283,16 @@
         <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64">
         <v>50</v>
@@ -11275,13 +11312,13 @@
         <v>298</v>
       </c>
       <c r="C65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F65">
         <v>149</v>
@@ -11298,16 +11335,16 @@
         <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E66" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F66">
         <v>149</v>
@@ -11324,16 +11361,16 @@
         <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F67">
         <v>17</v>
@@ -11342,7 +11379,7 @@
         <v>17</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -11350,16 +11387,16 @@
         <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F68">
         <v>1499</v>
@@ -11376,16 +11413,16 @@
         <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E69" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F69">
         <v>27</v>
@@ -11402,16 +11439,16 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C70" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E70" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F70">
         <v>17</v>
@@ -11428,19 +11465,19 @@
         <v>106</v>
       </c>
       <c r="B71" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D71" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E71" t="s">
         <v>38</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" ht="28.8" spans="1:8">
@@ -11448,19 +11485,19 @@
         <v>107</v>
       </c>
       <c r="B72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D72" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E72" t="s">
         <v>38</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -11468,19 +11505,19 @@
         <v>109</v>
       </c>
       <c r="B73" t="s">
+        <v>328</v>
+      </c>
+      <c r="C73" t="s">
         <v>327</v>
       </c>
-      <c r="C73" t="s">
-        <v>326</v>
-      </c>
       <c r="D73" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E73" t="s">
         <v>38</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74" ht="28.8" spans="1:8">
@@ -11488,19 +11525,19 @@
         <v>110</v>
       </c>
       <c r="B74" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C74" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D74" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E74" t="s">
         <v>38</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -11508,19 +11545,19 @@
         <v>113</v>
       </c>
       <c r="B75" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C75" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D75" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E75" t="s">
         <v>38</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -11528,19 +11565,19 @@
         <v>114</v>
       </c>
       <c r="B76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C76" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D76" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E76" t="s">
         <v>38</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -11548,16 +11585,16 @@
         <v>119</v>
       </c>
       <c r="B77" t="s">
+        <v>344</v>
+      </c>
+      <c r="C77" t="s">
         <v>341</v>
       </c>
-      <c r="C77" t="s">
-        <v>338</v>
-      </c>
       <c r="D77" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F77">
         <v>2800</v>
@@ -11574,16 +11611,16 @@
         <v>120</v>
       </c>
       <c r="B78" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C78" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F78">
         <v>950</v>
@@ -11600,19 +11637,19 @@
         <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C79" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E79" t="s">
         <v>38</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -11620,19 +11657,19 @@
         <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C80" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D80" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E80" t="s">
         <v>38</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -11640,19 +11677,19 @@
         <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C81" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D81" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E81" t="s">
         <v>38</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
